--- a/data/dai.xlsx
+++ b/data/dai.xlsx
@@ -429,1146 +429,1146 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HT29"/>
+  <dimension ref="A1:HT33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>subject</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>group</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>FP1-FP2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>FP1-F3</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>FP1-F4</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>FP1-F7</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>FP1-F8</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>FP1-FZ</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>FP1-C3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>FP1-C4</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>FP1-CZ</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>FP1-T3</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>FP1-T4</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>FP1-T5</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>FP1-T6</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>FP1-P3</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>FP1-P4</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>FP1-PZ</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>FP1-O1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>FP1-O2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>FP2-F3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>FP2-F4</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>FP2-F7</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>FP2-F8</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>FP2-FZ</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>FP2-C3</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>FP2-C4</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>FP2-CZ</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>FP2-T3</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>FP2-T4</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>FP2-T5</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>FP2-T6</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>FP2-P3</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>FP2-P4</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>FP2-PZ</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>FP2-O1</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>FP2-O2</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>F3-F4</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>F3-F7</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>F3-F8</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>F3-FZ</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>F3-C3</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>F3-C4</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>F3-CZ</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>F3-T3</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>F3-T4</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>F3-T5</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>F3-T6</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>F3-P3</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>F3-P4</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>F3-PZ</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>F3-O1</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>F3-O2</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>F4-F7</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>F4-F8</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>F4-FZ</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>F4-C3</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>F4-C4</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>F4-CZ</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>F4-T3</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>F4-T4</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>F4-T5</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>F4-T6</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>F4-P3</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>F4-P4</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>F4-PZ</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>F4-O1</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>F4-O2</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>F7-F8</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>F7-FZ</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>F7-C3</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>F7-C4</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>F7-CZ</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>F7-T3</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>F7-T4</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>F7-T5</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>F7-T6</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>F7-P3</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>F7-P4</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>F7-PZ</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>F7-O1</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>F7-O2</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>F8-FZ</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>F8-C3</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>F8-C4</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>F8-CZ</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>F8-T3</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>F8-T4</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>F8-T5</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>F8-T6</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>F8-P3</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>F8-P4</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>F8-PZ</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>F8-O1</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>F8-O2</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>FZ-C3</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>FZ-C4</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>FZ-CZ</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>FZ-T3</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>FZ-T4</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>FZ-T5</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>FZ-T6</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>FZ-P3</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>FZ-P4</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>FZ-PZ</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>FZ-O1</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>FZ-O2</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>C3-C4</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>C3-CZ</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>C3-T3</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>C3-T4</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>C3-T5</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>C3-T6</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>C3-P3</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>C3-P4</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>C3-PZ</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>C3-O1</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>C3-O2</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>C4-CZ</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>C4-T3</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>C4-T4</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>C4-T5</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>C4-T6</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>C4-P3</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>C4-P4</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>C4-PZ</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>C4-O1</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>C4-O2</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>CZ-T3</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>CZ-T4</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>CZ-T5</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>CZ-T6</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>CZ-P3</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>CZ-P4</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>CZ-PZ</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>CZ-O1</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>CZ-O2</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>T3-T4</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>T3-T5</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>T3-T6</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>T3-P3</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>T3-P4</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>T3-PZ</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>T3-O1</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>T3-O2</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>T4-T5</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>T4-T6</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>T4-P3</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>T4-P4</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>T4-PZ</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>T4-O1</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>T4-O2</t>
         </is>
       </c>
-      <c r="EW1" s="1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>T5-T6</t>
         </is>
       </c>
-      <c r="EX1" s="1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>T5-P3</t>
         </is>
       </c>
-      <c r="EY1" s="1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>T5-P4</t>
         </is>
       </c>
-      <c r="EZ1" s="1" t="inlineStr">
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>T5-PZ</t>
         </is>
       </c>
-      <c r="FA1" s="1" t="inlineStr">
+      <c r="FA1" t="inlineStr">
         <is>
           <t>T5-O1</t>
         </is>
       </c>
-      <c r="FB1" s="1" t="inlineStr">
+      <c r="FB1" t="inlineStr">
         <is>
           <t>T5-O2</t>
         </is>
       </c>
-      <c r="FC1" s="1" t="inlineStr">
+      <c r="FC1" t="inlineStr">
         <is>
           <t>T6-P3</t>
         </is>
       </c>
-      <c r="FD1" s="1" t="inlineStr">
+      <c r="FD1" t="inlineStr">
         <is>
           <t>T6-P4</t>
         </is>
       </c>
-      <c r="FE1" s="1" t="inlineStr">
+      <c r="FE1" t="inlineStr">
         <is>
           <t>T6-PZ</t>
         </is>
       </c>
-      <c r="FF1" s="1" t="inlineStr">
+      <c r="FF1" t="inlineStr">
         <is>
           <t>T6-O1</t>
         </is>
       </c>
-      <c r="FG1" s="1" t="inlineStr">
+      <c r="FG1" t="inlineStr">
         <is>
           <t>T6-O2</t>
         </is>
       </c>
-      <c r="FH1" s="1" t="inlineStr">
+      <c r="FH1" t="inlineStr">
         <is>
           <t>P3-P4</t>
         </is>
       </c>
-      <c r="FI1" s="1" t="inlineStr">
+      <c r="FI1" t="inlineStr">
         <is>
           <t>P3-PZ</t>
         </is>
       </c>
-      <c r="FJ1" s="1" t="inlineStr">
+      <c r="FJ1" t="inlineStr">
         <is>
           <t>P3-O1</t>
         </is>
       </c>
-      <c r="FK1" s="1" t="inlineStr">
+      <c r="FK1" t="inlineStr">
         <is>
           <t>P3-O2</t>
         </is>
       </c>
-      <c r="FL1" s="1" t="inlineStr">
+      <c r="FL1" t="inlineStr">
         <is>
           <t>P4-PZ</t>
         </is>
       </c>
-      <c r="FM1" s="1" t="inlineStr">
+      <c r="FM1" t="inlineStr">
         <is>
           <t>P4-O1</t>
         </is>
       </c>
-      <c r="FN1" s="1" t="inlineStr">
+      <c r="FN1" t="inlineStr">
         <is>
           <t>P4-O2</t>
         </is>
       </c>
-      <c r="FO1" s="1" t="inlineStr">
+      <c r="FO1" t="inlineStr">
         <is>
           <t>PZ-O1</t>
         </is>
       </c>
-      <c r="FP1" s="1" t="inlineStr">
+      <c r="FP1" t="inlineStr">
         <is>
           <t>PZ-O2</t>
         </is>
       </c>
-      <c r="FQ1" s="1" t="inlineStr">
+      <c r="FQ1" t="inlineStr">
         <is>
           <t>O1-O2</t>
         </is>
       </c>
-      <c r="FR1" s="1" t="inlineStr">
+      <c r="FR1" t="inlineStr">
         <is>
           <t>C3-F3</t>
         </is>
       </c>
-      <c r="FS1" s="1" t="inlineStr">
+      <c r="FS1" t="inlineStr">
         <is>
           <t>C3-F4</t>
         </is>
       </c>
-      <c r="FT1" s="1" t="inlineStr">
+      <c r="FT1" t="inlineStr">
         <is>
           <t>C3-F7</t>
         </is>
       </c>
-      <c r="FU1" s="1" t="inlineStr">
+      <c r="FU1" t="inlineStr">
         <is>
           <t>C3-F8</t>
         </is>
       </c>
-      <c r="FV1" s="1" t="inlineStr">
+      <c r="FV1" t="inlineStr">
         <is>
           <t>C3-FP1</t>
         </is>
       </c>
-      <c r="FW1" s="1" t="inlineStr">
+      <c r="FW1" t="inlineStr">
         <is>
           <t>C3-FP2</t>
         </is>
       </c>
-      <c r="FX1" s="1" t="inlineStr">
+      <c r="FX1" t="inlineStr">
         <is>
           <t>C3-FZ</t>
         </is>
       </c>
-      <c r="FY1" s="1" t="inlineStr">
+      <c r="FY1" t="inlineStr">
         <is>
           <t>C4-F3</t>
         </is>
       </c>
-      <c r="FZ1" s="1" t="inlineStr">
+      <c r="FZ1" t="inlineStr">
         <is>
           <t>C4-F4</t>
         </is>
       </c>
-      <c r="GA1" s="1" t="inlineStr">
+      <c r="GA1" t="inlineStr">
         <is>
           <t>C4-F7</t>
         </is>
       </c>
-      <c r="GB1" s="1" t="inlineStr">
+      <c r="GB1" t="inlineStr">
         <is>
           <t>C4-F8</t>
         </is>
       </c>
-      <c r="GC1" s="1" t="inlineStr">
+      <c r="GC1" t="inlineStr">
         <is>
           <t>C4-FP1</t>
         </is>
       </c>
-      <c r="GD1" s="1" t="inlineStr">
+      <c r="GD1" t="inlineStr">
         <is>
           <t>C4-FP2</t>
         </is>
       </c>
-      <c r="GE1" s="1" t="inlineStr">
+      <c r="GE1" t="inlineStr">
         <is>
           <t>C4-FZ</t>
         </is>
       </c>
-      <c r="GF1" s="1" t="inlineStr">
+      <c r="GF1" t="inlineStr">
         <is>
           <t>CZ-F3</t>
         </is>
       </c>
-      <c r="GG1" s="1" t="inlineStr">
+      <c r="GG1" t="inlineStr">
         <is>
           <t>CZ-F4</t>
         </is>
       </c>
-      <c r="GH1" s="1" t="inlineStr">
+      <c r="GH1" t="inlineStr">
         <is>
           <t>CZ-F7</t>
         </is>
       </c>
-      <c r="GI1" s="1" t="inlineStr">
+      <c r="GI1" t="inlineStr">
         <is>
           <t>CZ-F8</t>
         </is>
       </c>
-      <c r="GJ1" s="1" t="inlineStr">
+      <c r="GJ1" t="inlineStr">
         <is>
           <t>CZ-FP1</t>
         </is>
       </c>
-      <c r="GK1" s="1" t="inlineStr">
+      <c r="GK1" t="inlineStr">
         <is>
           <t>CZ-FP2</t>
         </is>
       </c>
-      <c r="GL1" s="1" t="inlineStr">
+      <c r="GL1" t="inlineStr">
         <is>
           <t>CZ-FZ</t>
         </is>
       </c>
-      <c r="GM1" s="1" t="inlineStr">
+      <c r="GM1" t="inlineStr">
         <is>
           <t>F3-FP1</t>
         </is>
       </c>
-      <c r="GN1" s="1" t="inlineStr">
+      <c r="GN1" t="inlineStr">
         <is>
           <t>F3-FP2</t>
         </is>
       </c>
-      <c r="GO1" s="1" t="inlineStr">
+      <c r="GO1" t="inlineStr">
         <is>
           <t>F4-FP1</t>
         </is>
       </c>
-      <c r="GP1" s="1" t="inlineStr">
+      <c r="GP1" t="inlineStr">
         <is>
           <t>F4-FP2</t>
         </is>
       </c>
-      <c r="GQ1" s="1" t="inlineStr">
+      <c r="GQ1" t="inlineStr">
         <is>
           <t>F7-FP1</t>
         </is>
       </c>
-      <c r="GR1" s="1" t="inlineStr">
+      <c r="GR1" t="inlineStr">
         <is>
           <t>F7-FP2</t>
         </is>
       </c>
-      <c r="GS1" s="1" t="inlineStr">
+      <c r="GS1" t="inlineStr">
         <is>
           <t>F8-FP1</t>
         </is>
       </c>
-      <c r="GT1" s="1" t="inlineStr">
+      <c r="GT1" t="inlineStr">
         <is>
           <t>F8-FP2</t>
         </is>
       </c>
-      <c r="GU1" s="1" t="inlineStr">
+      <c r="GU1" t="inlineStr">
         <is>
           <t>O1-P3</t>
         </is>
       </c>
-      <c r="GV1" s="1" t="inlineStr">
+      <c r="GV1" t="inlineStr">
         <is>
           <t>O1-P4</t>
         </is>
       </c>
-      <c r="GW1" s="1" t="inlineStr">
+      <c r="GW1" t="inlineStr">
         <is>
           <t>O1-PZ</t>
         </is>
       </c>
-      <c r="GX1" s="1" t="inlineStr">
+      <c r="GX1" t="inlineStr">
         <is>
           <t>O1-T3</t>
         </is>
       </c>
-      <c r="GY1" s="1" t="inlineStr">
+      <c r="GY1" t="inlineStr">
         <is>
           <t>O1-T4</t>
         </is>
       </c>
-      <c r="GZ1" s="1" t="inlineStr">
+      <c r="GZ1" t="inlineStr">
         <is>
           <t>O1-T5</t>
         </is>
       </c>
-      <c r="HA1" s="1" t="inlineStr">
+      <c r="HA1" t="inlineStr">
         <is>
           <t>O1-T6</t>
         </is>
       </c>
-      <c r="HB1" s="1" t="inlineStr">
+      <c r="HB1" t="inlineStr">
         <is>
           <t>O2-P3</t>
         </is>
       </c>
-      <c r="HC1" s="1" t="inlineStr">
+      <c r="HC1" t="inlineStr">
         <is>
           <t>O2-P4</t>
         </is>
       </c>
-      <c r="HD1" s="1" t="inlineStr">
+      <c r="HD1" t="inlineStr">
         <is>
           <t>O2-PZ</t>
         </is>
       </c>
-      <c r="HE1" s="1" t="inlineStr">
+      <c r="HE1" t="inlineStr">
         <is>
           <t>O2-T3</t>
         </is>
       </c>
-      <c r="HF1" s="1" t="inlineStr">
+      <c r="HF1" t="inlineStr">
         <is>
           <t>O2-T4</t>
         </is>
       </c>
-      <c r="HG1" s="1" t="inlineStr">
+      <c r="HG1" t="inlineStr">
         <is>
           <t>O2-T5</t>
         </is>
       </c>
-      <c r="HH1" s="1" t="inlineStr">
+      <c r="HH1" t="inlineStr">
         <is>
           <t>O2-T6</t>
         </is>
       </c>
-      <c r="HI1" s="1" t="inlineStr">
+      <c r="HI1" t="inlineStr">
         <is>
           <t>P3-T3</t>
         </is>
       </c>
-      <c r="HJ1" s="1" t="inlineStr">
+      <c r="HJ1" t="inlineStr">
         <is>
           <t>P3-T4</t>
         </is>
       </c>
-      <c r="HK1" s="1" t="inlineStr">
+      <c r="HK1" t="inlineStr">
         <is>
           <t>P3-T5</t>
         </is>
       </c>
-      <c r="HL1" s="1" t="inlineStr">
+      <c r="HL1" t="inlineStr">
         <is>
           <t>P3-T6</t>
         </is>
       </c>
-      <c r="HM1" s="1" t="inlineStr">
+      <c r="HM1" t="inlineStr">
         <is>
           <t>P4-T3</t>
         </is>
       </c>
-      <c r="HN1" s="1" t="inlineStr">
+      <c r="HN1" t="inlineStr">
         <is>
           <t>P4-T4</t>
         </is>
       </c>
-      <c r="HO1" s="1" t="inlineStr">
+      <c r="HO1" t="inlineStr">
         <is>
           <t>P4-T5</t>
         </is>
       </c>
-      <c r="HP1" s="1" t="inlineStr">
+      <c r="HP1" t="inlineStr">
         <is>
           <t>P4-T6</t>
         </is>
       </c>
-      <c r="HQ1" s="1" t="inlineStr">
+      <c r="HQ1" t="inlineStr">
         <is>
           <t>PZ-T3</t>
         </is>
       </c>
-      <c r="HR1" s="1" t="inlineStr">
+      <c r="HR1" t="inlineStr">
         <is>
           <t>PZ-T4</t>
         </is>
       </c>
-      <c r="HS1" s="1" t="inlineStr">
+      <c r="HS1" t="inlineStr">
         <is>
           <t>PZ-T5</t>
         </is>
       </c>
-      <c r="HT1" s="1" t="inlineStr">
+      <c r="HT1" t="inlineStr">
         <is>
           <t>PZ-T6</t>
         </is>
@@ -2098,6 +2098,171 @@
       <c r="FQ2" t="n">
         <v>-0.7371020284159587</v>
       </c>
+      <c r="FR2" t="n">
+        <v/>
+      </c>
+      <c r="FS2" t="n">
+        <v/>
+      </c>
+      <c r="FT2" t="n">
+        <v/>
+      </c>
+      <c r="FU2" t="n">
+        <v/>
+      </c>
+      <c r="FV2" t="n">
+        <v/>
+      </c>
+      <c r="FW2" t="n">
+        <v/>
+      </c>
+      <c r="FX2" t="n">
+        <v/>
+      </c>
+      <c r="FY2" t="n">
+        <v/>
+      </c>
+      <c r="FZ2" t="n">
+        <v/>
+      </c>
+      <c r="GA2" t="n">
+        <v/>
+      </c>
+      <c r="GB2" t="n">
+        <v/>
+      </c>
+      <c r="GC2" t="n">
+        <v/>
+      </c>
+      <c r="GD2" t="n">
+        <v/>
+      </c>
+      <c r="GE2" t="n">
+        <v/>
+      </c>
+      <c r="GF2" t="n">
+        <v/>
+      </c>
+      <c r="GG2" t="n">
+        <v/>
+      </c>
+      <c r="GH2" t="n">
+        <v/>
+      </c>
+      <c r="GI2" t="n">
+        <v/>
+      </c>
+      <c r="GJ2" t="n">
+        <v/>
+      </c>
+      <c r="GK2" t="n">
+        <v/>
+      </c>
+      <c r="GL2" t="n">
+        <v/>
+      </c>
+      <c r="GM2" t="n">
+        <v/>
+      </c>
+      <c r="GN2" t="n">
+        <v/>
+      </c>
+      <c r="GO2" t="n">
+        <v/>
+      </c>
+      <c r="GP2" t="n">
+        <v/>
+      </c>
+      <c r="GQ2" t="n">
+        <v/>
+      </c>
+      <c r="GR2" t="n">
+        <v/>
+      </c>
+      <c r="GS2" t="n">
+        <v/>
+      </c>
+      <c r="GT2" t="n">
+        <v/>
+      </c>
+      <c r="GU2" t="n">
+        <v/>
+      </c>
+      <c r="GV2" t="n">
+        <v/>
+      </c>
+      <c r="GW2" t="n">
+        <v/>
+      </c>
+      <c r="GX2" t="n">
+        <v/>
+      </c>
+      <c r="GY2" t="n">
+        <v/>
+      </c>
+      <c r="GZ2" t="n">
+        <v/>
+      </c>
+      <c r="HA2" t="n">
+        <v/>
+      </c>
+      <c r="HB2" t="n">
+        <v/>
+      </c>
+      <c r="HC2" t="n">
+        <v/>
+      </c>
+      <c r="HD2" t="n">
+        <v/>
+      </c>
+      <c r="HE2" t="n">
+        <v/>
+      </c>
+      <c r="HF2" t="n">
+        <v/>
+      </c>
+      <c r="HG2" t="n">
+        <v/>
+      </c>
+      <c r="HH2" t="n">
+        <v/>
+      </c>
+      <c r="HI2" t="n">
+        <v/>
+      </c>
+      <c r="HJ2" t="n">
+        <v/>
+      </c>
+      <c r="HK2" t="n">
+        <v/>
+      </c>
+      <c r="HL2" t="n">
+        <v/>
+      </c>
+      <c r="HM2" t="n">
+        <v/>
+      </c>
+      <c r="HN2" t="n">
+        <v/>
+      </c>
+      <c r="HO2" t="n">
+        <v/>
+      </c>
+      <c r="HP2" t="n">
+        <v/>
+      </c>
+      <c r="HQ2" t="n">
+        <v/>
+      </c>
+      <c r="HR2" t="n">
+        <v/>
+      </c>
+      <c r="HS2" t="n">
+        <v/>
+      </c>
+      <c r="HT2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2623,6 +2788,171 @@
       <c r="FQ3" t="n">
         <v>0.1068147391655407</v>
       </c>
+      <c r="FR3" t="n">
+        <v/>
+      </c>
+      <c r="FS3" t="n">
+        <v/>
+      </c>
+      <c r="FT3" t="n">
+        <v/>
+      </c>
+      <c r="FU3" t="n">
+        <v/>
+      </c>
+      <c r="FV3" t="n">
+        <v/>
+      </c>
+      <c r="FW3" t="n">
+        <v/>
+      </c>
+      <c r="FX3" t="n">
+        <v/>
+      </c>
+      <c r="FY3" t="n">
+        <v/>
+      </c>
+      <c r="FZ3" t="n">
+        <v/>
+      </c>
+      <c r="GA3" t="n">
+        <v/>
+      </c>
+      <c r="GB3" t="n">
+        <v/>
+      </c>
+      <c r="GC3" t="n">
+        <v/>
+      </c>
+      <c r="GD3" t="n">
+        <v/>
+      </c>
+      <c r="GE3" t="n">
+        <v/>
+      </c>
+      <c r="GF3" t="n">
+        <v/>
+      </c>
+      <c r="GG3" t="n">
+        <v/>
+      </c>
+      <c r="GH3" t="n">
+        <v/>
+      </c>
+      <c r="GI3" t="n">
+        <v/>
+      </c>
+      <c r="GJ3" t="n">
+        <v/>
+      </c>
+      <c r="GK3" t="n">
+        <v/>
+      </c>
+      <c r="GL3" t="n">
+        <v/>
+      </c>
+      <c r="GM3" t="n">
+        <v/>
+      </c>
+      <c r="GN3" t="n">
+        <v/>
+      </c>
+      <c r="GO3" t="n">
+        <v/>
+      </c>
+      <c r="GP3" t="n">
+        <v/>
+      </c>
+      <c r="GQ3" t="n">
+        <v/>
+      </c>
+      <c r="GR3" t="n">
+        <v/>
+      </c>
+      <c r="GS3" t="n">
+        <v/>
+      </c>
+      <c r="GT3" t="n">
+        <v/>
+      </c>
+      <c r="GU3" t="n">
+        <v/>
+      </c>
+      <c r="GV3" t="n">
+        <v/>
+      </c>
+      <c r="GW3" t="n">
+        <v/>
+      </c>
+      <c r="GX3" t="n">
+        <v/>
+      </c>
+      <c r="GY3" t="n">
+        <v/>
+      </c>
+      <c r="GZ3" t="n">
+        <v/>
+      </c>
+      <c r="HA3" t="n">
+        <v/>
+      </c>
+      <c r="HB3" t="n">
+        <v/>
+      </c>
+      <c r="HC3" t="n">
+        <v/>
+      </c>
+      <c r="HD3" t="n">
+        <v/>
+      </c>
+      <c r="HE3" t="n">
+        <v/>
+      </c>
+      <c r="HF3" t="n">
+        <v/>
+      </c>
+      <c r="HG3" t="n">
+        <v/>
+      </c>
+      <c r="HH3" t="n">
+        <v/>
+      </c>
+      <c r="HI3" t="n">
+        <v/>
+      </c>
+      <c r="HJ3" t="n">
+        <v/>
+      </c>
+      <c r="HK3" t="n">
+        <v/>
+      </c>
+      <c r="HL3" t="n">
+        <v/>
+      </c>
+      <c r="HM3" t="n">
+        <v/>
+      </c>
+      <c r="HN3" t="n">
+        <v/>
+      </c>
+      <c r="HO3" t="n">
+        <v/>
+      </c>
+      <c r="HP3" t="n">
+        <v/>
+      </c>
+      <c r="HQ3" t="n">
+        <v/>
+      </c>
+      <c r="HR3" t="n">
+        <v/>
+      </c>
+      <c r="HS3" t="n">
+        <v/>
+      </c>
+      <c r="HT3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3148,6 +3478,171 @@
       <c r="FQ4" t="n">
         <v>-0.2544032714365221</v>
       </c>
+      <c r="FR4" t="n">
+        <v/>
+      </c>
+      <c r="FS4" t="n">
+        <v/>
+      </c>
+      <c r="FT4" t="n">
+        <v/>
+      </c>
+      <c r="FU4" t="n">
+        <v/>
+      </c>
+      <c r="FV4" t="n">
+        <v/>
+      </c>
+      <c r="FW4" t="n">
+        <v/>
+      </c>
+      <c r="FX4" t="n">
+        <v/>
+      </c>
+      <c r="FY4" t="n">
+        <v/>
+      </c>
+      <c r="FZ4" t="n">
+        <v/>
+      </c>
+      <c r="GA4" t="n">
+        <v/>
+      </c>
+      <c r="GB4" t="n">
+        <v/>
+      </c>
+      <c r="GC4" t="n">
+        <v/>
+      </c>
+      <c r="GD4" t="n">
+        <v/>
+      </c>
+      <c r="GE4" t="n">
+        <v/>
+      </c>
+      <c r="GF4" t="n">
+        <v/>
+      </c>
+      <c r="GG4" t="n">
+        <v/>
+      </c>
+      <c r="GH4" t="n">
+        <v/>
+      </c>
+      <c r="GI4" t="n">
+        <v/>
+      </c>
+      <c r="GJ4" t="n">
+        <v/>
+      </c>
+      <c r="GK4" t="n">
+        <v/>
+      </c>
+      <c r="GL4" t="n">
+        <v/>
+      </c>
+      <c r="GM4" t="n">
+        <v/>
+      </c>
+      <c r="GN4" t="n">
+        <v/>
+      </c>
+      <c r="GO4" t="n">
+        <v/>
+      </c>
+      <c r="GP4" t="n">
+        <v/>
+      </c>
+      <c r="GQ4" t="n">
+        <v/>
+      </c>
+      <c r="GR4" t="n">
+        <v/>
+      </c>
+      <c r="GS4" t="n">
+        <v/>
+      </c>
+      <c r="GT4" t="n">
+        <v/>
+      </c>
+      <c r="GU4" t="n">
+        <v/>
+      </c>
+      <c r="GV4" t="n">
+        <v/>
+      </c>
+      <c r="GW4" t="n">
+        <v/>
+      </c>
+      <c r="GX4" t="n">
+        <v/>
+      </c>
+      <c r="GY4" t="n">
+        <v/>
+      </c>
+      <c r="GZ4" t="n">
+        <v/>
+      </c>
+      <c r="HA4" t="n">
+        <v/>
+      </c>
+      <c r="HB4" t="n">
+        <v/>
+      </c>
+      <c r="HC4" t="n">
+        <v/>
+      </c>
+      <c r="HD4" t="n">
+        <v/>
+      </c>
+      <c r="HE4" t="n">
+        <v/>
+      </c>
+      <c r="HF4" t="n">
+        <v/>
+      </c>
+      <c r="HG4" t="n">
+        <v/>
+      </c>
+      <c r="HH4" t="n">
+        <v/>
+      </c>
+      <c r="HI4" t="n">
+        <v/>
+      </c>
+      <c r="HJ4" t="n">
+        <v/>
+      </c>
+      <c r="HK4" t="n">
+        <v/>
+      </c>
+      <c r="HL4" t="n">
+        <v/>
+      </c>
+      <c r="HM4" t="n">
+        <v/>
+      </c>
+      <c r="HN4" t="n">
+        <v/>
+      </c>
+      <c r="HO4" t="n">
+        <v/>
+      </c>
+      <c r="HP4" t="n">
+        <v/>
+      </c>
+      <c r="HQ4" t="n">
+        <v/>
+      </c>
+      <c r="HR4" t="n">
+        <v/>
+      </c>
+      <c r="HS4" t="n">
+        <v/>
+      </c>
+      <c r="HT4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3673,6 +4168,171 @@
       <c r="FQ5" t="n">
         <v>-0.4102353222184988</v>
       </c>
+      <c r="FR5" t="n">
+        <v/>
+      </c>
+      <c r="FS5" t="n">
+        <v/>
+      </c>
+      <c r="FT5" t="n">
+        <v/>
+      </c>
+      <c r="FU5" t="n">
+        <v/>
+      </c>
+      <c r="FV5" t="n">
+        <v/>
+      </c>
+      <c r="FW5" t="n">
+        <v/>
+      </c>
+      <c r="FX5" t="n">
+        <v/>
+      </c>
+      <c r="FY5" t="n">
+        <v/>
+      </c>
+      <c r="FZ5" t="n">
+        <v/>
+      </c>
+      <c r="GA5" t="n">
+        <v/>
+      </c>
+      <c r="GB5" t="n">
+        <v/>
+      </c>
+      <c r="GC5" t="n">
+        <v/>
+      </c>
+      <c r="GD5" t="n">
+        <v/>
+      </c>
+      <c r="GE5" t="n">
+        <v/>
+      </c>
+      <c r="GF5" t="n">
+        <v/>
+      </c>
+      <c r="GG5" t="n">
+        <v/>
+      </c>
+      <c r="GH5" t="n">
+        <v/>
+      </c>
+      <c r="GI5" t="n">
+        <v/>
+      </c>
+      <c r="GJ5" t="n">
+        <v/>
+      </c>
+      <c r="GK5" t="n">
+        <v/>
+      </c>
+      <c r="GL5" t="n">
+        <v/>
+      </c>
+      <c r="GM5" t="n">
+        <v/>
+      </c>
+      <c r="GN5" t="n">
+        <v/>
+      </c>
+      <c r="GO5" t="n">
+        <v/>
+      </c>
+      <c r="GP5" t="n">
+        <v/>
+      </c>
+      <c r="GQ5" t="n">
+        <v/>
+      </c>
+      <c r="GR5" t="n">
+        <v/>
+      </c>
+      <c r="GS5" t="n">
+        <v/>
+      </c>
+      <c r="GT5" t="n">
+        <v/>
+      </c>
+      <c r="GU5" t="n">
+        <v/>
+      </c>
+      <c r="GV5" t="n">
+        <v/>
+      </c>
+      <c r="GW5" t="n">
+        <v/>
+      </c>
+      <c r="GX5" t="n">
+        <v/>
+      </c>
+      <c r="GY5" t="n">
+        <v/>
+      </c>
+      <c r="GZ5" t="n">
+        <v/>
+      </c>
+      <c r="HA5" t="n">
+        <v/>
+      </c>
+      <c r="HB5" t="n">
+        <v/>
+      </c>
+      <c r="HC5" t="n">
+        <v/>
+      </c>
+      <c r="HD5" t="n">
+        <v/>
+      </c>
+      <c r="HE5" t="n">
+        <v/>
+      </c>
+      <c r="HF5" t="n">
+        <v/>
+      </c>
+      <c r="HG5" t="n">
+        <v/>
+      </c>
+      <c r="HH5" t="n">
+        <v/>
+      </c>
+      <c r="HI5" t="n">
+        <v/>
+      </c>
+      <c r="HJ5" t="n">
+        <v/>
+      </c>
+      <c r="HK5" t="n">
+        <v/>
+      </c>
+      <c r="HL5" t="n">
+        <v/>
+      </c>
+      <c r="HM5" t="n">
+        <v/>
+      </c>
+      <c r="HN5" t="n">
+        <v/>
+      </c>
+      <c r="HO5" t="n">
+        <v/>
+      </c>
+      <c r="HP5" t="n">
+        <v/>
+      </c>
+      <c r="HQ5" t="n">
+        <v/>
+      </c>
+      <c r="HR5" t="n">
+        <v/>
+      </c>
+      <c r="HS5" t="n">
+        <v/>
+      </c>
+      <c r="HT5" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4198,6 +4858,171 @@
       <c r="FQ6" t="n">
         <v>0.3292308457946104</v>
       </c>
+      <c r="FR6" t="n">
+        <v/>
+      </c>
+      <c r="FS6" t="n">
+        <v/>
+      </c>
+      <c r="FT6" t="n">
+        <v/>
+      </c>
+      <c r="FU6" t="n">
+        <v/>
+      </c>
+      <c r="FV6" t="n">
+        <v/>
+      </c>
+      <c r="FW6" t="n">
+        <v/>
+      </c>
+      <c r="FX6" t="n">
+        <v/>
+      </c>
+      <c r="FY6" t="n">
+        <v/>
+      </c>
+      <c r="FZ6" t="n">
+        <v/>
+      </c>
+      <c r="GA6" t="n">
+        <v/>
+      </c>
+      <c r="GB6" t="n">
+        <v/>
+      </c>
+      <c r="GC6" t="n">
+        <v/>
+      </c>
+      <c r="GD6" t="n">
+        <v/>
+      </c>
+      <c r="GE6" t="n">
+        <v/>
+      </c>
+      <c r="GF6" t="n">
+        <v/>
+      </c>
+      <c r="GG6" t="n">
+        <v/>
+      </c>
+      <c r="GH6" t="n">
+        <v/>
+      </c>
+      <c r="GI6" t="n">
+        <v/>
+      </c>
+      <c r="GJ6" t="n">
+        <v/>
+      </c>
+      <c r="GK6" t="n">
+        <v/>
+      </c>
+      <c r="GL6" t="n">
+        <v/>
+      </c>
+      <c r="GM6" t="n">
+        <v/>
+      </c>
+      <c r="GN6" t="n">
+        <v/>
+      </c>
+      <c r="GO6" t="n">
+        <v/>
+      </c>
+      <c r="GP6" t="n">
+        <v/>
+      </c>
+      <c r="GQ6" t="n">
+        <v/>
+      </c>
+      <c r="GR6" t="n">
+        <v/>
+      </c>
+      <c r="GS6" t="n">
+        <v/>
+      </c>
+      <c r="GT6" t="n">
+        <v/>
+      </c>
+      <c r="GU6" t="n">
+        <v/>
+      </c>
+      <c r="GV6" t="n">
+        <v/>
+      </c>
+      <c r="GW6" t="n">
+        <v/>
+      </c>
+      <c r="GX6" t="n">
+        <v/>
+      </c>
+      <c r="GY6" t="n">
+        <v/>
+      </c>
+      <c r="GZ6" t="n">
+        <v/>
+      </c>
+      <c r="HA6" t="n">
+        <v/>
+      </c>
+      <c r="HB6" t="n">
+        <v/>
+      </c>
+      <c r="HC6" t="n">
+        <v/>
+      </c>
+      <c r="HD6" t="n">
+        <v/>
+      </c>
+      <c r="HE6" t="n">
+        <v/>
+      </c>
+      <c r="HF6" t="n">
+        <v/>
+      </c>
+      <c r="HG6" t="n">
+        <v/>
+      </c>
+      <c r="HH6" t="n">
+        <v/>
+      </c>
+      <c r="HI6" t="n">
+        <v/>
+      </c>
+      <c r="HJ6" t="n">
+        <v/>
+      </c>
+      <c r="HK6" t="n">
+        <v/>
+      </c>
+      <c r="HL6" t="n">
+        <v/>
+      </c>
+      <c r="HM6" t="n">
+        <v/>
+      </c>
+      <c r="HN6" t="n">
+        <v/>
+      </c>
+      <c r="HO6" t="n">
+        <v/>
+      </c>
+      <c r="HP6" t="n">
+        <v/>
+      </c>
+      <c r="HQ6" t="n">
+        <v/>
+      </c>
+      <c r="HR6" t="n">
+        <v/>
+      </c>
+      <c r="HS6" t="n">
+        <v/>
+      </c>
+      <c r="HT6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5413,6 +6238,171 @@
       <c r="FQ8" t="n">
         <v>0.5512235283397969</v>
       </c>
+      <c r="FR8" t="n">
+        <v/>
+      </c>
+      <c r="FS8" t="n">
+        <v/>
+      </c>
+      <c r="FT8" t="n">
+        <v/>
+      </c>
+      <c r="FU8" t="n">
+        <v/>
+      </c>
+      <c r="FV8" t="n">
+        <v/>
+      </c>
+      <c r="FW8" t="n">
+        <v/>
+      </c>
+      <c r="FX8" t="n">
+        <v/>
+      </c>
+      <c r="FY8" t="n">
+        <v/>
+      </c>
+      <c r="FZ8" t="n">
+        <v/>
+      </c>
+      <c r="GA8" t="n">
+        <v/>
+      </c>
+      <c r="GB8" t="n">
+        <v/>
+      </c>
+      <c r="GC8" t="n">
+        <v/>
+      </c>
+      <c r="GD8" t="n">
+        <v/>
+      </c>
+      <c r="GE8" t="n">
+        <v/>
+      </c>
+      <c r="GF8" t="n">
+        <v/>
+      </c>
+      <c r="GG8" t="n">
+        <v/>
+      </c>
+      <c r="GH8" t="n">
+        <v/>
+      </c>
+      <c r="GI8" t="n">
+        <v/>
+      </c>
+      <c r="GJ8" t="n">
+        <v/>
+      </c>
+      <c r="GK8" t="n">
+        <v/>
+      </c>
+      <c r="GL8" t="n">
+        <v/>
+      </c>
+      <c r="GM8" t="n">
+        <v/>
+      </c>
+      <c r="GN8" t="n">
+        <v/>
+      </c>
+      <c r="GO8" t="n">
+        <v/>
+      </c>
+      <c r="GP8" t="n">
+        <v/>
+      </c>
+      <c r="GQ8" t="n">
+        <v/>
+      </c>
+      <c r="GR8" t="n">
+        <v/>
+      </c>
+      <c r="GS8" t="n">
+        <v/>
+      </c>
+      <c r="GT8" t="n">
+        <v/>
+      </c>
+      <c r="GU8" t="n">
+        <v/>
+      </c>
+      <c r="GV8" t="n">
+        <v/>
+      </c>
+      <c r="GW8" t="n">
+        <v/>
+      </c>
+      <c r="GX8" t="n">
+        <v/>
+      </c>
+      <c r="GY8" t="n">
+        <v/>
+      </c>
+      <c r="GZ8" t="n">
+        <v/>
+      </c>
+      <c r="HA8" t="n">
+        <v/>
+      </c>
+      <c r="HB8" t="n">
+        <v/>
+      </c>
+      <c r="HC8" t="n">
+        <v/>
+      </c>
+      <c r="HD8" t="n">
+        <v/>
+      </c>
+      <c r="HE8" t="n">
+        <v/>
+      </c>
+      <c r="HF8" t="n">
+        <v/>
+      </c>
+      <c r="HG8" t="n">
+        <v/>
+      </c>
+      <c r="HH8" t="n">
+        <v/>
+      </c>
+      <c r="HI8" t="n">
+        <v/>
+      </c>
+      <c r="HJ8" t="n">
+        <v/>
+      </c>
+      <c r="HK8" t="n">
+        <v/>
+      </c>
+      <c r="HL8" t="n">
+        <v/>
+      </c>
+      <c r="HM8" t="n">
+        <v/>
+      </c>
+      <c r="HN8" t="n">
+        <v/>
+      </c>
+      <c r="HO8" t="n">
+        <v/>
+      </c>
+      <c r="HP8" t="n">
+        <v/>
+      </c>
+      <c r="HQ8" t="n">
+        <v/>
+      </c>
+      <c r="HR8" t="n">
+        <v/>
+      </c>
+      <c r="HS8" t="n">
+        <v/>
+      </c>
+      <c r="HT8" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5938,6 +6928,171 @@
       <c r="FQ9" t="n">
         <v>-0.4502622550470381</v>
       </c>
+      <c r="FR9" t="n">
+        <v/>
+      </c>
+      <c r="FS9" t="n">
+        <v/>
+      </c>
+      <c r="FT9" t="n">
+        <v/>
+      </c>
+      <c r="FU9" t="n">
+        <v/>
+      </c>
+      <c r="FV9" t="n">
+        <v/>
+      </c>
+      <c r="FW9" t="n">
+        <v/>
+      </c>
+      <c r="FX9" t="n">
+        <v/>
+      </c>
+      <c r="FY9" t="n">
+        <v/>
+      </c>
+      <c r="FZ9" t="n">
+        <v/>
+      </c>
+      <c r="GA9" t="n">
+        <v/>
+      </c>
+      <c r="GB9" t="n">
+        <v/>
+      </c>
+      <c r="GC9" t="n">
+        <v/>
+      </c>
+      <c r="GD9" t="n">
+        <v/>
+      </c>
+      <c r="GE9" t="n">
+        <v/>
+      </c>
+      <c r="GF9" t="n">
+        <v/>
+      </c>
+      <c r="GG9" t="n">
+        <v/>
+      </c>
+      <c r="GH9" t="n">
+        <v/>
+      </c>
+      <c r="GI9" t="n">
+        <v/>
+      </c>
+      <c r="GJ9" t="n">
+        <v/>
+      </c>
+      <c r="GK9" t="n">
+        <v/>
+      </c>
+      <c r="GL9" t="n">
+        <v/>
+      </c>
+      <c r="GM9" t="n">
+        <v/>
+      </c>
+      <c r="GN9" t="n">
+        <v/>
+      </c>
+      <c r="GO9" t="n">
+        <v/>
+      </c>
+      <c r="GP9" t="n">
+        <v/>
+      </c>
+      <c r="GQ9" t="n">
+        <v/>
+      </c>
+      <c r="GR9" t="n">
+        <v/>
+      </c>
+      <c r="GS9" t="n">
+        <v/>
+      </c>
+      <c r="GT9" t="n">
+        <v/>
+      </c>
+      <c r="GU9" t="n">
+        <v/>
+      </c>
+      <c r="GV9" t="n">
+        <v/>
+      </c>
+      <c r="GW9" t="n">
+        <v/>
+      </c>
+      <c r="GX9" t="n">
+        <v/>
+      </c>
+      <c r="GY9" t="n">
+        <v/>
+      </c>
+      <c r="GZ9" t="n">
+        <v/>
+      </c>
+      <c r="HA9" t="n">
+        <v/>
+      </c>
+      <c r="HB9" t="n">
+        <v/>
+      </c>
+      <c r="HC9" t="n">
+        <v/>
+      </c>
+      <c r="HD9" t="n">
+        <v/>
+      </c>
+      <c r="HE9" t="n">
+        <v/>
+      </c>
+      <c r="HF9" t="n">
+        <v/>
+      </c>
+      <c r="HG9" t="n">
+        <v/>
+      </c>
+      <c r="HH9" t="n">
+        <v/>
+      </c>
+      <c r="HI9" t="n">
+        <v/>
+      </c>
+      <c r="HJ9" t="n">
+        <v/>
+      </c>
+      <c r="HK9" t="n">
+        <v/>
+      </c>
+      <c r="HL9" t="n">
+        <v/>
+      </c>
+      <c r="HM9" t="n">
+        <v/>
+      </c>
+      <c r="HN9" t="n">
+        <v/>
+      </c>
+      <c r="HO9" t="n">
+        <v/>
+      </c>
+      <c r="HP9" t="n">
+        <v/>
+      </c>
+      <c r="HQ9" t="n">
+        <v/>
+      </c>
+      <c r="HR9" t="n">
+        <v/>
+      </c>
+      <c r="HS9" t="n">
+        <v/>
+      </c>
+      <c r="HT9" t="n">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6463,6 +7618,171 @@
       <c r="FQ10" t="n">
         <v>-0.1906231644902757</v>
       </c>
+      <c r="FR10" t="n">
+        <v/>
+      </c>
+      <c r="FS10" t="n">
+        <v/>
+      </c>
+      <c r="FT10" t="n">
+        <v/>
+      </c>
+      <c r="FU10" t="n">
+        <v/>
+      </c>
+      <c r="FV10" t="n">
+        <v/>
+      </c>
+      <c r="FW10" t="n">
+        <v/>
+      </c>
+      <c r="FX10" t="n">
+        <v/>
+      </c>
+      <c r="FY10" t="n">
+        <v/>
+      </c>
+      <c r="FZ10" t="n">
+        <v/>
+      </c>
+      <c r="GA10" t="n">
+        <v/>
+      </c>
+      <c r="GB10" t="n">
+        <v/>
+      </c>
+      <c r="GC10" t="n">
+        <v/>
+      </c>
+      <c r="GD10" t="n">
+        <v/>
+      </c>
+      <c r="GE10" t="n">
+        <v/>
+      </c>
+      <c r="GF10" t="n">
+        <v/>
+      </c>
+      <c r="GG10" t="n">
+        <v/>
+      </c>
+      <c r="GH10" t="n">
+        <v/>
+      </c>
+      <c r="GI10" t="n">
+        <v/>
+      </c>
+      <c r="GJ10" t="n">
+        <v/>
+      </c>
+      <c r="GK10" t="n">
+        <v/>
+      </c>
+      <c r="GL10" t="n">
+        <v/>
+      </c>
+      <c r="GM10" t="n">
+        <v/>
+      </c>
+      <c r="GN10" t="n">
+        <v/>
+      </c>
+      <c r="GO10" t="n">
+        <v/>
+      </c>
+      <c r="GP10" t="n">
+        <v/>
+      </c>
+      <c r="GQ10" t="n">
+        <v/>
+      </c>
+      <c r="GR10" t="n">
+        <v/>
+      </c>
+      <c r="GS10" t="n">
+        <v/>
+      </c>
+      <c r="GT10" t="n">
+        <v/>
+      </c>
+      <c r="GU10" t="n">
+        <v/>
+      </c>
+      <c r="GV10" t="n">
+        <v/>
+      </c>
+      <c r="GW10" t="n">
+        <v/>
+      </c>
+      <c r="GX10" t="n">
+        <v/>
+      </c>
+      <c r="GY10" t="n">
+        <v/>
+      </c>
+      <c r="GZ10" t="n">
+        <v/>
+      </c>
+      <c r="HA10" t="n">
+        <v/>
+      </c>
+      <c r="HB10" t="n">
+        <v/>
+      </c>
+      <c r="HC10" t="n">
+        <v/>
+      </c>
+      <c r="HD10" t="n">
+        <v/>
+      </c>
+      <c r="HE10" t="n">
+        <v/>
+      </c>
+      <c r="HF10" t="n">
+        <v/>
+      </c>
+      <c r="HG10" t="n">
+        <v/>
+      </c>
+      <c r="HH10" t="n">
+        <v/>
+      </c>
+      <c r="HI10" t="n">
+        <v/>
+      </c>
+      <c r="HJ10" t="n">
+        <v/>
+      </c>
+      <c r="HK10" t="n">
+        <v/>
+      </c>
+      <c r="HL10" t="n">
+        <v/>
+      </c>
+      <c r="HM10" t="n">
+        <v/>
+      </c>
+      <c r="HN10" t="n">
+        <v/>
+      </c>
+      <c r="HO10" t="n">
+        <v/>
+      </c>
+      <c r="HP10" t="n">
+        <v/>
+      </c>
+      <c r="HQ10" t="n">
+        <v/>
+      </c>
+      <c r="HR10" t="n">
+        <v/>
+      </c>
+      <c r="HS10" t="n">
+        <v/>
+      </c>
+      <c r="HT10" t="n">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6988,6 +8308,171 @@
       <c r="FQ11" t="n">
         <v>-0.08791550220812365</v>
       </c>
+      <c r="FR11" t="n">
+        <v/>
+      </c>
+      <c r="FS11" t="n">
+        <v/>
+      </c>
+      <c r="FT11" t="n">
+        <v/>
+      </c>
+      <c r="FU11" t="n">
+        <v/>
+      </c>
+      <c r="FV11" t="n">
+        <v/>
+      </c>
+      <c r="FW11" t="n">
+        <v/>
+      </c>
+      <c r="FX11" t="n">
+        <v/>
+      </c>
+      <c r="FY11" t="n">
+        <v/>
+      </c>
+      <c r="FZ11" t="n">
+        <v/>
+      </c>
+      <c r="GA11" t="n">
+        <v/>
+      </c>
+      <c r="GB11" t="n">
+        <v/>
+      </c>
+      <c r="GC11" t="n">
+        <v/>
+      </c>
+      <c r="GD11" t="n">
+        <v/>
+      </c>
+      <c r="GE11" t="n">
+        <v/>
+      </c>
+      <c r="GF11" t="n">
+        <v/>
+      </c>
+      <c r="GG11" t="n">
+        <v/>
+      </c>
+      <c r="GH11" t="n">
+        <v/>
+      </c>
+      <c r="GI11" t="n">
+        <v/>
+      </c>
+      <c r="GJ11" t="n">
+        <v/>
+      </c>
+      <c r="GK11" t="n">
+        <v/>
+      </c>
+      <c r="GL11" t="n">
+        <v/>
+      </c>
+      <c r="GM11" t="n">
+        <v/>
+      </c>
+      <c r="GN11" t="n">
+        <v/>
+      </c>
+      <c r="GO11" t="n">
+        <v/>
+      </c>
+      <c r="GP11" t="n">
+        <v/>
+      </c>
+      <c r="GQ11" t="n">
+        <v/>
+      </c>
+      <c r="GR11" t="n">
+        <v/>
+      </c>
+      <c r="GS11" t="n">
+        <v/>
+      </c>
+      <c r="GT11" t="n">
+        <v/>
+      </c>
+      <c r="GU11" t="n">
+        <v/>
+      </c>
+      <c r="GV11" t="n">
+        <v/>
+      </c>
+      <c r="GW11" t="n">
+        <v/>
+      </c>
+      <c r="GX11" t="n">
+        <v/>
+      </c>
+      <c r="GY11" t="n">
+        <v/>
+      </c>
+      <c r="GZ11" t="n">
+        <v/>
+      </c>
+      <c r="HA11" t="n">
+        <v/>
+      </c>
+      <c r="HB11" t="n">
+        <v/>
+      </c>
+      <c r="HC11" t="n">
+        <v/>
+      </c>
+      <c r="HD11" t="n">
+        <v/>
+      </c>
+      <c r="HE11" t="n">
+        <v/>
+      </c>
+      <c r="HF11" t="n">
+        <v/>
+      </c>
+      <c r="HG11" t="n">
+        <v/>
+      </c>
+      <c r="HH11" t="n">
+        <v/>
+      </c>
+      <c r="HI11" t="n">
+        <v/>
+      </c>
+      <c r="HJ11" t="n">
+        <v/>
+      </c>
+      <c r="HK11" t="n">
+        <v/>
+      </c>
+      <c r="HL11" t="n">
+        <v/>
+      </c>
+      <c r="HM11" t="n">
+        <v/>
+      </c>
+      <c r="HN11" t="n">
+        <v/>
+      </c>
+      <c r="HO11" t="n">
+        <v/>
+      </c>
+      <c r="HP11" t="n">
+        <v/>
+      </c>
+      <c r="HQ11" t="n">
+        <v/>
+      </c>
+      <c r="HR11" t="n">
+        <v/>
+      </c>
+      <c r="HS11" t="n">
+        <v/>
+      </c>
+      <c r="HT11" t="n">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7513,6 +8998,171 @@
       <c r="FQ12" t="n">
         <v>0.5587432185999456</v>
       </c>
+      <c r="FR12" t="n">
+        <v/>
+      </c>
+      <c r="FS12" t="n">
+        <v/>
+      </c>
+      <c r="FT12" t="n">
+        <v/>
+      </c>
+      <c r="FU12" t="n">
+        <v/>
+      </c>
+      <c r="FV12" t="n">
+        <v/>
+      </c>
+      <c r="FW12" t="n">
+        <v/>
+      </c>
+      <c r="FX12" t="n">
+        <v/>
+      </c>
+      <c r="FY12" t="n">
+        <v/>
+      </c>
+      <c r="FZ12" t="n">
+        <v/>
+      </c>
+      <c r="GA12" t="n">
+        <v/>
+      </c>
+      <c r="GB12" t="n">
+        <v/>
+      </c>
+      <c r="GC12" t="n">
+        <v/>
+      </c>
+      <c r="GD12" t="n">
+        <v/>
+      </c>
+      <c r="GE12" t="n">
+        <v/>
+      </c>
+      <c r="GF12" t="n">
+        <v/>
+      </c>
+      <c r="GG12" t="n">
+        <v/>
+      </c>
+      <c r="GH12" t="n">
+        <v/>
+      </c>
+      <c r="GI12" t="n">
+        <v/>
+      </c>
+      <c r="GJ12" t="n">
+        <v/>
+      </c>
+      <c r="GK12" t="n">
+        <v/>
+      </c>
+      <c r="GL12" t="n">
+        <v/>
+      </c>
+      <c r="GM12" t="n">
+        <v/>
+      </c>
+      <c r="GN12" t="n">
+        <v/>
+      </c>
+      <c r="GO12" t="n">
+        <v/>
+      </c>
+      <c r="GP12" t="n">
+        <v/>
+      </c>
+      <c r="GQ12" t="n">
+        <v/>
+      </c>
+      <c r="GR12" t="n">
+        <v/>
+      </c>
+      <c r="GS12" t="n">
+        <v/>
+      </c>
+      <c r="GT12" t="n">
+        <v/>
+      </c>
+      <c r="GU12" t="n">
+        <v/>
+      </c>
+      <c r="GV12" t="n">
+        <v/>
+      </c>
+      <c r="GW12" t="n">
+        <v/>
+      </c>
+      <c r="GX12" t="n">
+        <v/>
+      </c>
+      <c r="GY12" t="n">
+        <v/>
+      </c>
+      <c r="GZ12" t="n">
+        <v/>
+      </c>
+      <c r="HA12" t="n">
+        <v/>
+      </c>
+      <c r="HB12" t="n">
+        <v/>
+      </c>
+      <c r="HC12" t="n">
+        <v/>
+      </c>
+      <c r="HD12" t="n">
+        <v/>
+      </c>
+      <c r="HE12" t="n">
+        <v/>
+      </c>
+      <c r="HF12" t="n">
+        <v/>
+      </c>
+      <c r="HG12" t="n">
+        <v/>
+      </c>
+      <c r="HH12" t="n">
+        <v/>
+      </c>
+      <c r="HI12" t="n">
+        <v/>
+      </c>
+      <c r="HJ12" t="n">
+        <v/>
+      </c>
+      <c r="HK12" t="n">
+        <v/>
+      </c>
+      <c r="HL12" t="n">
+        <v/>
+      </c>
+      <c r="HM12" t="n">
+        <v/>
+      </c>
+      <c r="HN12" t="n">
+        <v/>
+      </c>
+      <c r="HO12" t="n">
+        <v/>
+      </c>
+      <c r="HP12" t="n">
+        <v/>
+      </c>
+      <c r="HQ12" t="n">
+        <v/>
+      </c>
+      <c r="HR12" t="n">
+        <v/>
+      </c>
+      <c r="HS12" t="n">
+        <v/>
+      </c>
+      <c r="HT12" t="n">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8038,6 +9688,171 @@
       <c r="FQ13" t="n">
         <v>0.1277821319325558</v>
       </c>
+      <c r="FR13" t="n">
+        <v/>
+      </c>
+      <c r="FS13" t="n">
+        <v/>
+      </c>
+      <c r="FT13" t="n">
+        <v/>
+      </c>
+      <c r="FU13" t="n">
+        <v/>
+      </c>
+      <c r="FV13" t="n">
+        <v/>
+      </c>
+      <c r="FW13" t="n">
+        <v/>
+      </c>
+      <c r="FX13" t="n">
+        <v/>
+      </c>
+      <c r="FY13" t="n">
+        <v/>
+      </c>
+      <c r="FZ13" t="n">
+        <v/>
+      </c>
+      <c r="GA13" t="n">
+        <v/>
+      </c>
+      <c r="GB13" t="n">
+        <v/>
+      </c>
+      <c r="GC13" t="n">
+        <v/>
+      </c>
+      <c r="GD13" t="n">
+        <v/>
+      </c>
+      <c r="GE13" t="n">
+        <v/>
+      </c>
+      <c r="GF13" t="n">
+        <v/>
+      </c>
+      <c r="GG13" t="n">
+        <v/>
+      </c>
+      <c r="GH13" t="n">
+        <v/>
+      </c>
+      <c r="GI13" t="n">
+        <v/>
+      </c>
+      <c r="GJ13" t="n">
+        <v/>
+      </c>
+      <c r="GK13" t="n">
+        <v/>
+      </c>
+      <c r="GL13" t="n">
+        <v/>
+      </c>
+      <c r="GM13" t="n">
+        <v/>
+      </c>
+      <c r="GN13" t="n">
+        <v/>
+      </c>
+      <c r="GO13" t="n">
+        <v/>
+      </c>
+      <c r="GP13" t="n">
+        <v/>
+      </c>
+      <c r="GQ13" t="n">
+        <v/>
+      </c>
+      <c r="GR13" t="n">
+        <v/>
+      </c>
+      <c r="GS13" t="n">
+        <v/>
+      </c>
+      <c r="GT13" t="n">
+        <v/>
+      </c>
+      <c r="GU13" t="n">
+        <v/>
+      </c>
+      <c r="GV13" t="n">
+        <v/>
+      </c>
+      <c r="GW13" t="n">
+        <v/>
+      </c>
+      <c r="GX13" t="n">
+        <v/>
+      </c>
+      <c r="GY13" t="n">
+        <v/>
+      </c>
+      <c r="GZ13" t="n">
+        <v/>
+      </c>
+      <c r="HA13" t="n">
+        <v/>
+      </c>
+      <c r="HB13" t="n">
+        <v/>
+      </c>
+      <c r="HC13" t="n">
+        <v/>
+      </c>
+      <c r="HD13" t="n">
+        <v/>
+      </c>
+      <c r="HE13" t="n">
+        <v/>
+      </c>
+      <c r="HF13" t="n">
+        <v/>
+      </c>
+      <c r="HG13" t="n">
+        <v/>
+      </c>
+      <c r="HH13" t="n">
+        <v/>
+      </c>
+      <c r="HI13" t="n">
+        <v/>
+      </c>
+      <c r="HJ13" t="n">
+        <v/>
+      </c>
+      <c r="HK13" t="n">
+        <v/>
+      </c>
+      <c r="HL13" t="n">
+        <v/>
+      </c>
+      <c r="HM13" t="n">
+        <v/>
+      </c>
+      <c r="HN13" t="n">
+        <v/>
+      </c>
+      <c r="HO13" t="n">
+        <v/>
+      </c>
+      <c r="HP13" t="n">
+        <v/>
+      </c>
+      <c r="HQ13" t="n">
+        <v/>
+      </c>
+      <c r="HR13" t="n">
+        <v/>
+      </c>
+      <c r="HS13" t="n">
+        <v/>
+      </c>
+      <c r="HT13" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8563,6 +10378,171 @@
       <c r="FQ14" t="n">
         <v>-0.1584053052692175</v>
       </c>
+      <c r="FR14" t="n">
+        <v/>
+      </c>
+      <c r="FS14" t="n">
+        <v/>
+      </c>
+      <c r="FT14" t="n">
+        <v/>
+      </c>
+      <c r="FU14" t="n">
+        <v/>
+      </c>
+      <c r="FV14" t="n">
+        <v/>
+      </c>
+      <c r="FW14" t="n">
+        <v/>
+      </c>
+      <c r="FX14" t="n">
+        <v/>
+      </c>
+      <c r="FY14" t="n">
+        <v/>
+      </c>
+      <c r="FZ14" t="n">
+        <v/>
+      </c>
+      <c r="GA14" t="n">
+        <v/>
+      </c>
+      <c r="GB14" t="n">
+        <v/>
+      </c>
+      <c r="GC14" t="n">
+        <v/>
+      </c>
+      <c r="GD14" t="n">
+        <v/>
+      </c>
+      <c r="GE14" t="n">
+        <v/>
+      </c>
+      <c r="GF14" t="n">
+        <v/>
+      </c>
+      <c r="GG14" t="n">
+        <v/>
+      </c>
+      <c r="GH14" t="n">
+        <v/>
+      </c>
+      <c r="GI14" t="n">
+        <v/>
+      </c>
+      <c r="GJ14" t="n">
+        <v/>
+      </c>
+      <c r="GK14" t="n">
+        <v/>
+      </c>
+      <c r="GL14" t="n">
+        <v/>
+      </c>
+      <c r="GM14" t="n">
+        <v/>
+      </c>
+      <c r="GN14" t="n">
+        <v/>
+      </c>
+      <c r="GO14" t="n">
+        <v/>
+      </c>
+      <c r="GP14" t="n">
+        <v/>
+      </c>
+      <c r="GQ14" t="n">
+        <v/>
+      </c>
+      <c r="GR14" t="n">
+        <v/>
+      </c>
+      <c r="GS14" t="n">
+        <v/>
+      </c>
+      <c r="GT14" t="n">
+        <v/>
+      </c>
+      <c r="GU14" t="n">
+        <v/>
+      </c>
+      <c r="GV14" t="n">
+        <v/>
+      </c>
+      <c r="GW14" t="n">
+        <v/>
+      </c>
+      <c r="GX14" t="n">
+        <v/>
+      </c>
+      <c r="GY14" t="n">
+        <v/>
+      </c>
+      <c r="GZ14" t="n">
+        <v/>
+      </c>
+      <c r="HA14" t="n">
+        <v/>
+      </c>
+      <c r="HB14" t="n">
+        <v/>
+      </c>
+      <c r="HC14" t="n">
+        <v/>
+      </c>
+      <c r="HD14" t="n">
+        <v/>
+      </c>
+      <c r="HE14" t="n">
+        <v/>
+      </c>
+      <c r="HF14" t="n">
+        <v/>
+      </c>
+      <c r="HG14" t="n">
+        <v/>
+      </c>
+      <c r="HH14" t="n">
+        <v/>
+      </c>
+      <c r="HI14" t="n">
+        <v/>
+      </c>
+      <c r="HJ14" t="n">
+        <v/>
+      </c>
+      <c r="HK14" t="n">
+        <v/>
+      </c>
+      <c r="HL14" t="n">
+        <v/>
+      </c>
+      <c r="HM14" t="n">
+        <v/>
+      </c>
+      <c r="HN14" t="n">
+        <v/>
+      </c>
+      <c r="HO14" t="n">
+        <v/>
+      </c>
+      <c r="HP14" t="n">
+        <v/>
+      </c>
+      <c r="HQ14" t="n">
+        <v/>
+      </c>
+      <c r="HR14" t="n">
+        <v/>
+      </c>
+      <c r="HS14" t="n">
+        <v/>
+      </c>
+      <c r="HT14" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9088,6 +11068,171 @@
       <c r="FQ15" t="n">
         <v>0.08378227922349502</v>
       </c>
+      <c r="FR15" t="n">
+        <v/>
+      </c>
+      <c r="FS15" t="n">
+        <v/>
+      </c>
+      <c r="FT15" t="n">
+        <v/>
+      </c>
+      <c r="FU15" t="n">
+        <v/>
+      </c>
+      <c r="FV15" t="n">
+        <v/>
+      </c>
+      <c r="FW15" t="n">
+        <v/>
+      </c>
+      <c r="FX15" t="n">
+        <v/>
+      </c>
+      <c r="FY15" t="n">
+        <v/>
+      </c>
+      <c r="FZ15" t="n">
+        <v/>
+      </c>
+      <c r="GA15" t="n">
+        <v/>
+      </c>
+      <c r="GB15" t="n">
+        <v/>
+      </c>
+      <c r="GC15" t="n">
+        <v/>
+      </c>
+      <c r="GD15" t="n">
+        <v/>
+      </c>
+      <c r="GE15" t="n">
+        <v/>
+      </c>
+      <c r="GF15" t="n">
+        <v/>
+      </c>
+      <c r="GG15" t="n">
+        <v/>
+      </c>
+      <c r="GH15" t="n">
+        <v/>
+      </c>
+      <c r="GI15" t="n">
+        <v/>
+      </c>
+      <c r="GJ15" t="n">
+        <v/>
+      </c>
+      <c r="GK15" t="n">
+        <v/>
+      </c>
+      <c r="GL15" t="n">
+        <v/>
+      </c>
+      <c r="GM15" t="n">
+        <v/>
+      </c>
+      <c r="GN15" t="n">
+        <v/>
+      </c>
+      <c r="GO15" t="n">
+        <v/>
+      </c>
+      <c r="GP15" t="n">
+        <v/>
+      </c>
+      <c r="GQ15" t="n">
+        <v/>
+      </c>
+      <c r="GR15" t="n">
+        <v/>
+      </c>
+      <c r="GS15" t="n">
+        <v/>
+      </c>
+      <c r="GT15" t="n">
+        <v/>
+      </c>
+      <c r="GU15" t="n">
+        <v/>
+      </c>
+      <c r="GV15" t="n">
+        <v/>
+      </c>
+      <c r="GW15" t="n">
+        <v/>
+      </c>
+      <c r="GX15" t="n">
+        <v/>
+      </c>
+      <c r="GY15" t="n">
+        <v/>
+      </c>
+      <c r="GZ15" t="n">
+        <v/>
+      </c>
+      <c r="HA15" t="n">
+        <v/>
+      </c>
+      <c r="HB15" t="n">
+        <v/>
+      </c>
+      <c r="HC15" t="n">
+        <v/>
+      </c>
+      <c r="HD15" t="n">
+        <v/>
+      </c>
+      <c r="HE15" t="n">
+        <v/>
+      </c>
+      <c r="HF15" t="n">
+        <v/>
+      </c>
+      <c r="HG15" t="n">
+        <v/>
+      </c>
+      <c r="HH15" t="n">
+        <v/>
+      </c>
+      <c r="HI15" t="n">
+        <v/>
+      </c>
+      <c r="HJ15" t="n">
+        <v/>
+      </c>
+      <c r="HK15" t="n">
+        <v/>
+      </c>
+      <c r="HL15" t="n">
+        <v/>
+      </c>
+      <c r="HM15" t="n">
+        <v/>
+      </c>
+      <c r="HN15" t="n">
+        <v/>
+      </c>
+      <c r="HO15" t="n">
+        <v/>
+      </c>
+      <c r="HP15" t="n">
+        <v/>
+      </c>
+      <c r="HQ15" t="n">
+        <v/>
+      </c>
+      <c r="HR15" t="n">
+        <v/>
+      </c>
+      <c r="HS15" t="n">
+        <v/>
+      </c>
+      <c r="HT15" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9613,6 +11758,171 @@
       <c r="FQ16" t="n">
         <v>-0.08667048269107763</v>
       </c>
+      <c r="FR16" t="n">
+        <v/>
+      </c>
+      <c r="FS16" t="n">
+        <v/>
+      </c>
+      <c r="FT16" t="n">
+        <v/>
+      </c>
+      <c r="FU16" t="n">
+        <v/>
+      </c>
+      <c r="FV16" t="n">
+        <v/>
+      </c>
+      <c r="FW16" t="n">
+        <v/>
+      </c>
+      <c r="FX16" t="n">
+        <v/>
+      </c>
+      <c r="FY16" t="n">
+        <v/>
+      </c>
+      <c r="FZ16" t="n">
+        <v/>
+      </c>
+      <c r="GA16" t="n">
+        <v/>
+      </c>
+      <c r="GB16" t="n">
+        <v/>
+      </c>
+      <c r="GC16" t="n">
+        <v/>
+      </c>
+      <c r="GD16" t="n">
+        <v/>
+      </c>
+      <c r="GE16" t="n">
+        <v/>
+      </c>
+      <c r="GF16" t="n">
+        <v/>
+      </c>
+      <c r="GG16" t="n">
+        <v/>
+      </c>
+      <c r="GH16" t="n">
+        <v/>
+      </c>
+      <c r="GI16" t="n">
+        <v/>
+      </c>
+      <c r="GJ16" t="n">
+        <v/>
+      </c>
+      <c r="GK16" t="n">
+        <v/>
+      </c>
+      <c r="GL16" t="n">
+        <v/>
+      </c>
+      <c r="GM16" t="n">
+        <v/>
+      </c>
+      <c r="GN16" t="n">
+        <v/>
+      </c>
+      <c r="GO16" t="n">
+        <v/>
+      </c>
+      <c r="GP16" t="n">
+        <v/>
+      </c>
+      <c r="GQ16" t="n">
+        <v/>
+      </c>
+      <c r="GR16" t="n">
+        <v/>
+      </c>
+      <c r="GS16" t="n">
+        <v/>
+      </c>
+      <c r="GT16" t="n">
+        <v/>
+      </c>
+      <c r="GU16" t="n">
+        <v/>
+      </c>
+      <c r="GV16" t="n">
+        <v/>
+      </c>
+      <c r="GW16" t="n">
+        <v/>
+      </c>
+      <c r="GX16" t="n">
+        <v/>
+      </c>
+      <c r="GY16" t="n">
+        <v/>
+      </c>
+      <c r="GZ16" t="n">
+        <v/>
+      </c>
+      <c r="HA16" t="n">
+        <v/>
+      </c>
+      <c r="HB16" t="n">
+        <v/>
+      </c>
+      <c r="HC16" t="n">
+        <v/>
+      </c>
+      <c r="HD16" t="n">
+        <v/>
+      </c>
+      <c r="HE16" t="n">
+        <v/>
+      </c>
+      <c r="HF16" t="n">
+        <v/>
+      </c>
+      <c r="HG16" t="n">
+        <v/>
+      </c>
+      <c r="HH16" t="n">
+        <v/>
+      </c>
+      <c r="HI16" t="n">
+        <v/>
+      </c>
+      <c r="HJ16" t="n">
+        <v/>
+      </c>
+      <c r="HK16" t="n">
+        <v/>
+      </c>
+      <c r="HL16" t="n">
+        <v/>
+      </c>
+      <c r="HM16" t="n">
+        <v/>
+      </c>
+      <c r="HN16" t="n">
+        <v/>
+      </c>
+      <c r="HO16" t="n">
+        <v/>
+      </c>
+      <c r="HP16" t="n">
+        <v/>
+      </c>
+      <c r="HQ16" t="n">
+        <v/>
+      </c>
+      <c r="HR16" t="n">
+        <v/>
+      </c>
+      <c r="HS16" t="n">
+        <v/>
+      </c>
+      <c r="HT16" t="n">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10138,6 +12448,171 @@
       <c r="FQ17" t="n">
         <v>-0.5774529465686317</v>
       </c>
+      <c r="FR17" t="n">
+        <v/>
+      </c>
+      <c r="FS17" t="n">
+        <v/>
+      </c>
+      <c r="FT17" t="n">
+        <v/>
+      </c>
+      <c r="FU17" t="n">
+        <v/>
+      </c>
+      <c r="FV17" t="n">
+        <v/>
+      </c>
+      <c r="FW17" t="n">
+        <v/>
+      </c>
+      <c r="FX17" t="n">
+        <v/>
+      </c>
+      <c r="FY17" t="n">
+        <v/>
+      </c>
+      <c r="FZ17" t="n">
+        <v/>
+      </c>
+      <c r="GA17" t="n">
+        <v/>
+      </c>
+      <c r="GB17" t="n">
+        <v/>
+      </c>
+      <c r="GC17" t="n">
+        <v/>
+      </c>
+      <c r="GD17" t="n">
+        <v/>
+      </c>
+      <c r="GE17" t="n">
+        <v/>
+      </c>
+      <c r="GF17" t="n">
+        <v/>
+      </c>
+      <c r="GG17" t="n">
+        <v/>
+      </c>
+      <c r="GH17" t="n">
+        <v/>
+      </c>
+      <c r="GI17" t="n">
+        <v/>
+      </c>
+      <c r="GJ17" t="n">
+        <v/>
+      </c>
+      <c r="GK17" t="n">
+        <v/>
+      </c>
+      <c r="GL17" t="n">
+        <v/>
+      </c>
+      <c r="GM17" t="n">
+        <v/>
+      </c>
+      <c r="GN17" t="n">
+        <v/>
+      </c>
+      <c r="GO17" t="n">
+        <v/>
+      </c>
+      <c r="GP17" t="n">
+        <v/>
+      </c>
+      <c r="GQ17" t="n">
+        <v/>
+      </c>
+      <c r="GR17" t="n">
+        <v/>
+      </c>
+      <c r="GS17" t="n">
+        <v/>
+      </c>
+      <c r="GT17" t="n">
+        <v/>
+      </c>
+      <c r="GU17" t="n">
+        <v/>
+      </c>
+      <c r="GV17" t="n">
+        <v/>
+      </c>
+      <c r="GW17" t="n">
+        <v/>
+      </c>
+      <c r="GX17" t="n">
+        <v/>
+      </c>
+      <c r="GY17" t="n">
+        <v/>
+      </c>
+      <c r="GZ17" t="n">
+        <v/>
+      </c>
+      <c r="HA17" t="n">
+        <v/>
+      </c>
+      <c r="HB17" t="n">
+        <v/>
+      </c>
+      <c r="HC17" t="n">
+        <v/>
+      </c>
+      <c r="HD17" t="n">
+        <v/>
+      </c>
+      <c r="HE17" t="n">
+        <v/>
+      </c>
+      <c r="HF17" t="n">
+        <v/>
+      </c>
+      <c r="HG17" t="n">
+        <v/>
+      </c>
+      <c r="HH17" t="n">
+        <v/>
+      </c>
+      <c r="HI17" t="n">
+        <v/>
+      </c>
+      <c r="HJ17" t="n">
+        <v/>
+      </c>
+      <c r="HK17" t="n">
+        <v/>
+      </c>
+      <c r="HL17" t="n">
+        <v/>
+      </c>
+      <c r="HM17" t="n">
+        <v/>
+      </c>
+      <c r="HN17" t="n">
+        <v/>
+      </c>
+      <c r="HO17" t="n">
+        <v/>
+      </c>
+      <c r="HP17" t="n">
+        <v/>
+      </c>
+      <c r="HQ17" t="n">
+        <v/>
+      </c>
+      <c r="HR17" t="n">
+        <v/>
+      </c>
+      <c r="HS17" t="n">
+        <v/>
+      </c>
+      <c r="HT17" t="n">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10663,6 +13138,171 @@
       <c r="FQ18" t="n">
         <v>-0.1370165525664384</v>
       </c>
+      <c r="FR18" t="n">
+        <v/>
+      </c>
+      <c r="FS18" t="n">
+        <v/>
+      </c>
+      <c r="FT18" t="n">
+        <v/>
+      </c>
+      <c r="FU18" t="n">
+        <v/>
+      </c>
+      <c r="FV18" t="n">
+        <v/>
+      </c>
+      <c r="FW18" t="n">
+        <v/>
+      </c>
+      <c r="FX18" t="n">
+        <v/>
+      </c>
+      <c r="FY18" t="n">
+        <v/>
+      </c>
+      <c r="FZ18" t="n">
+        <v/>
+      </c>
+      <c r="GA18" t="n">
+        <v/>
+      </c>
+      <c r="GB18" t="n">
+        <v/>
+      </c>
+      <c r="GC18" t="n">
+        <v/>
+      </c>
+      <c r="GD18" t="n">
+        <v/>
+      </c>
+      <c r="GE18" t="n">
+        <v/>
+      </c>
+      <c r="GF18" t="n">
+        <v/>
+      </c>
+      <c r="GG18" t="n">
+        <v/>
+      </c>
+      <c r="GH18" t="n">
+        <v/>
+      </c>
+      <c r="GI18" t="n">
+        <v/>
+      </c>
+      <c r="GJ18" t="n">
+        <v/>
+      </c>
+      <c r="GK18" t="n">
+        <v/>
+      </c>
+      <c r="GL18" t="n">
+        <v/>
+      </c>
+      <c r="GM18" t="n">
+        <v/>
+      </c>
+      <c r="GN18" t="n">
+        <v/>
+      </c>
+      <c r="GO18" t="n">
+        <v/>
+      </c>
+      <c r="GP18" t="n">
+        <v/>
+      </c>
+      <c r="GQ18" t="n">
+        <v/>
+      </c>
+      <c r="GR18" t="n">
+        <v/>
+      </c>
+      <c r="GS18" t="n">
+        <v/>
+      </c>
+      <c r="GT18" t="n">
+        <v/>
+      </c>
+      <c r="GU18" t="n">
+        <v/>
+      </c>
+      <c r="GV18" t="n">
+        <v/>
+      </c>
+      <c r="GW18" t="n">
+        <v/>
+      </c>
+      <c r="GX18" t="n">
+        <v/>
+      </c>
+      <c r="GY18" t="n">
+        <v/>
+      </c>
+      <c r="GZ18" t="n">
+        <v/>
+      </c>
+      <c r="HA18" t="n">
+        <v/>
+      </c>
+      <c r="HB18" t="n">
+        <v/>
+      </c>
+      <c r="HC18" t="n">
+        <v/>
+      </c>
+      <c r="HD18" t="n">
+        <v/>
+      </c>
+      <c r="HE18" t="n">
+        <v/>
+      </c>
+      <c r="HF18" t="n">
+        <v/>
+      </c>
+      <c r="HG18" t="n">
+        <v/>
+      </c>
+      <c r="HH18" t="n">
+        <v/>
+      </c>
+      <c r="HI18" t="n">
+        <v/>
+      </c>
+      <c r="HJ18" t="n">
+        <v/>
+      </c>
+      <c r="HK18" t="n">
+        <v/>
+      </c>
+      <c r="HL18" t="n">
+        <v/>
+      </c>
+      <c r="HM18" t="n">
+        <v/>
+      </c>
+      <c r="HN18" t="n">
+        <v/>
+      </c>
+      <c r="HO18" t="n">
+        <v/>
+      </c>
+      <c r="HP18" t="n">
+        <v/>
+      </c>
+      <c r="HQ18" t="n">
+        <v/>
+      </c>
+      <c r="HR18" t="n">
+        <v/>
+      </c>
+      <c r="HS18" t="n">
+        <v/>
+      </c>
+      <c r="HT18" t="n">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11188,6 +13828,171 @@
       <c r="FQ19" t="n">
         <v>-0.1577383731879544</v>
       </c>
+      <c r="FR19" t="n">
+        <v/>
+      </c>
+      <c r="FS19" t="n">
+        <v/>
+      </c>
+      <c r="FT19" t="n">
+        <v/>
+      </c>
+      <c r="FU19" t="n">
+        <v/>
+      </c>
+      <c r="FV19" t="n">
+        <v/>
+      </c>
+      <c r="FW19" t="n">
+        <v/>
+      </c>
+      <c r="FX19" t="n">
+        <v/>
+      </c>
+      <c r="FY19" t="n">
+        <v/>
+      </c>
+      <c r="FZ19" t="n">
+        <v/>
+      </c>
+      <c r="GA19" t="n">
+        <v/>
+      </c>
+      <c r="GB19" t="n">
+        <v/>
+      </c>
+      <c r="GC19" t="n">
+        <v/>
+      </c>
+      <c r="GD19" t="n">
+        <v/>
+      </c>
+      <c r="GE19" t="n">
+        <v/>
+      </c>
+      <c r="GF19" t="n">
+        <v/>
+      </c>
+      <c r="GG19" t="n">
+        <v/>
+      </c>
+      <c r="GH19" t="n">
+        <v/>
+      </c>
+      <c r="GI19" t="n">
+        <v/>
+      </c>
+      <c r="GJ19" t="n">
+        <v/>
+      </c>
+      <c r="GK19" t="n">
+        <v/>
+      </c>
+      <c r="GL19" t="n">
+        <v/>
+      </c>
+      <c r="GM19" t="n">
+        <v/>
+      </c>
+      <c r="GN19" t="n">
+        <v/>
+      </c>
+      <c r="GO19" t="n">
+        <v/>
+      </c>
+      <c r="GP19" t="n">
+        <v/>
+      </c>
+      <c r="GQ19" t="n">
+        <v/>
+      </c>
+      <c r="GR19" t="n">
+        <v/>
+      </c>
+      <c r="GS19" t="n">
+        <v/>
+      </c>
+      <c r="GT19" t="n">
+        <v/>
+      </c>
+      <c r="GU19" t="n">
+        <v/>
+      </c>
+      <c r="GV19" t="n">
+        <v/>
+      </c>
+      <c r="GW19" t="n">
+        <v/>
+      </c>
+      <c r="GX19" t="n">
+        <v/>
+      </c>
+      <c r="GY19" t="n">
+        <v/>
+      </c>
+      <c r="GZ19" t="n">
+        <v/>
+      </c>
+      <c r="HA19" t="n">
+        <v/>
+      </c>
+      <c r="HB19" t="n">
+        <v/>
+      </c>
+      <c r="HC19" t="n">
+        <v/>
+      </c>
+      <c r="HD19" t="n">
+        <v/>
+      </c>
+      <c r="HE19" t="n">
+        <v/>
+      </c>
+      <c r="HF19" t="n">
+        <v/>
+      </c>
+      <c r="HG19" t="n">
+        <v/>
+      </c>
+      <c r="HH19" t="n">
+        <v/>
+      </c>
+      <c r="HI19" t="n">
+        <v/>
+      </c>
+      <c r="HJ19" t="n">
+        <v/>
+      </c>
+      <c r="HK19" t="n">
+        <v/>
+      </c>
+      <c r="HL19" t="n">
+        <v/>
+      </c>
+      <c r="HM19" t="n">
+        <v/>
+      </c>
+      <c r="HN19" t="n">
+        <v/>
+      </c>
+      <c r="HO19" t="n">
+        <v/>
+      </c>
+      <c r="HP19" t="n">
+        <v/>
+      </c>
+      <c r="HQ19" t="n">
+        <v/>
+      </c>
+      <c r="HR19" t="n">
+        <v/>
+      </c>
+      <c r="HS19" t="n">
+        <v/>
+      </c>
+      <c r="HT19" t="n">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11713,6 +14518,171 @@
       <c r="FQ20" t="n">
         <v>0.4066428727431683</v>
       </c>
+      <c r="FR20" t="n">
+        <v/>
+      </c>
+      <c r="FS20" t="n">
+        <v/>
+      </c>
+      <c r="FT20" t="n">
+        <v/>
+      </c>
+      <c r="FU20" t="n">
+        <v/>
+      </c>
+      <c r="FV20" t="n">
+        <v/>
+      </c>
+      <c r="FW20" t="n">
+        <v/>
+      </c>
+      <c r="FX20" t="n">
+        <v/>
+      </c>
+      <c r="FY20" t="n">
+        <v/>
+      </c>
+      <c r="FZ20" t="n">
+        <v/>
+      </c>
+      <c r="GA20" t="n">
+        <v/>
+      </c>
+      <c r="GB20" t="n">
+        <v/>
+      </c>
+      <c r="GC20" t="n">
+        <v/>
+      </c>
+      <c r="GD20" t="n">
+        <v/>
+      </c>
+      <c r="GE20" t="n">
+        <v/>
+      </c>
+      <c r="GF20" t="n">
+        <v/>
+      </c>
+      <c r="GG20" t="n">
+        <v/>
+      </c>
+      <c r="GH20" t="n">
+        <v/>
+      </c>
+      <c r="GI20" t="n">
+        <v/>
+      </c>
+      <c r="GJ20" t="n">
+        <v/>
+      </c>
+      <c r="GK20" t="n">
+        <v/>
+      </c>
+      <c r="GL20" t="n">
+        <v/>
+      </c>
+      <c r="GM20" t="n">
+        <v/>
+      </c>
+      <c r="GN20" t="n">
+        <v/>
+      </c>
+      <c r="GO20" t="n">
+        <v/>
+      </c>
+      <c r="GP20" t="n">
+        <v/>
+      </c>
+      <c r="GQ20" t="n">
+        <v/>
+      </c>
+      <c r="GR20" t="n">
+        <v/>
+      </c>
+      <c r="GS20" t="n">
+        <v/>
+      </c>
+      <c r="GT20" t="n">
+        <v/>
+      </c>
+      <c r="GU20" t="n">
+        <v/>
+      </c>
+      <c r="GV20" t="n">
+        <v/>
+      </c>
+      <c r="GW20" t="n">
+        <v/>
+      </c>
+      <c r="GX20" t="n">
+        <v/>
+      </c>
+      <c r="GY20" t="n">
+        <v/>
+      </c>
+      <c r="GZ20" t="n">
+        <v/>
+      </c>
+      <c r="HA20" t="n">
+        <v/>
+      </c>
+      <c r="HB20" t="n">
+        <v/>
+      </c>
+      <c r="HC20" t="n">
+        <v/>
+      </c>
+      <c r="HD20" t="n">
+        <v/>
+      </c>
+      <c r="HE20" t="n">
+        <v/>
+      </c>
+      <c r="HF20" t="n">
+        <v/>
+      </c>
+      <c r="HG20" t="n">
+        <v/>
+      </c>
+      <c r="HH20" t="n">
+        <v/>
+      </c>
+      <c r="HI20" t="n">
+        <v/>
+      </c>
+      <c r="HJ20" t="n">
+        <v/>
+      </c>
+      <c r="HK20" t="n">
+        <v/>
+      </c>
+      <c r="HL20" t="n">
+        <v/>
+      </c>
+      <c r="HM20" t="n">
+        <v/>
+      </c>
+      <c r="HN20" t="n">
+        <v/>
+      </c>
+      <c r="HO20" t="n">
+        <v/>
+      </c>
+      <c r="HP20" t="n">
+        <v/>
+      </c>
+      <c r="HQ20" t="n">
+        <v/>
+      </c>
+      <c r="HR20" t="n">
+        <v/>
+      </c>
+      <c r="HS20" t="n">
+        <v/>
+      </c>
+      <c r="HT20" t="n">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -12238,6 +15208,171 @@
       <c r="FQ21" t="n">
         <v>-0.0401329404308022</v>
       </c>
+      <c r="FR21" t="n">
+        <v/>
+      </c>
+      <c r="FS21" t="n">
+        <v/>
+      </c>
+      <c r="FT21" t="n">
+        <v/>
+      </c>
+      <c r="FU21" t="n">
+        <v/>
+      </c>
+      <c r="FV21" t="n">
+        <v/>
+      </c>
+      <c r="FW21" t="n">
+        <v/>
+      </c>
+      <c r="FX21" t="n">
+        <v/>
+      </c>
+      <c r="FY21" t="n">
+        <v/>
+      </c>
+      <c r="FZ21" t="n">
+        <v/>
+      </c>
+      <c r="GA21" t="n">
+        <v/>
+      </c>
+      <c r="GB21" t="n">
+        <v/>
+      </c>
+      <c r="GC21" t="n">
+        <v/>
+      </c>
+      <c r="GD21" t="n">
+        <v/>
+      </c>
+      <c r="GE21" t="n">
+        <v/>
+      </c>
+      <c r="GF21" t="n">
+        <v/>
+      </c>
+      <c r="GG21" t="n">
+        <v/>
+      </c>
+      <c r="GH21" t="n">
+        <v/>
+      </c>
+      <c r="GI21" t="n">
+        <v/>
+      </c>
+      <c r="GJ21" t="n">
+        <v/>
+      </c>
+      <c r="GK21" t="n">
+        <v/>
+      </c>
+      <c r="GL21" t="n">
+        <v/>
+      </c>
+      <c r="GM21" t="n">
+        <v/>
+      </c>
+      <c r="GN21" t="n">
+        <v/>
+      </c>
+      <c r="GO21" t="n">
+        <v/>
+      </c>
+      <c r="GP21" t="n">
+        <v/>
+      </c>
+      <c r="GQ21" t="n">
+        <v/>
+      </c>
+      <c r="GR21" t="n">
+        <v/>
+      </c>
+      <c r="GS21" t="n">
+        <v/>
+      </c>
+      <c r="GT21" t="n">
+        <v/>
+      </c>
+      <c r="GU21" t="n">
+        <v/>
+      </c>
+      <c r="GV21" t="n">
+        <v/>
+      </c>
+      <c r="GW21" t="n">
+        <v/>
+      </c>
+      <c r="GX21" t="n">
+        <v/>
+      </c>
+      <c r="GY21" t="n">
+        <v/>
+      </c>
+      <c r="GZ21" t="n">
+        <v/>
+      </c>
+      <c r="HA21" t="n">
+        <v/>
+      </c>
+      <c r="HB21" t="n">
+        <v/>
+      </c>
+      <c r="HC21" t="n">
+        <v/>
+      </c>
+      <c r="HD21" t="n">
+        <v/>
+      </c>
+      <c r="HE21" t="n">
+        <v/>
+      </c>
+      <c r="HF21" t="n">
+        <v/>
+      </c>
+      <c r="HG21" t="n">
+        <v/>
+      </c>
+      <c r="HH21" t="n">
+        <v/>
+      </c>
+      <c r="HI21" t="n">
+        <v/>
+      </c>
+      <c r="HJ21" t="n">
+        <v/>
+      </c>
+      <c r="HK21" t="n">
+        <v/>
+      </c>
+      <c r="HL21" t="n">
+        <v/>
+      </c>
+      <c r="HM21" t="n">
+        <v/>
+      </c>
+      <c r="HN21" t="n">
+        <v/>
+      </c>
+      <c r="HO21" t="n">
+        <v/>
+      </c>
+      <c r="HP21" t="n">
+        <v/>
+      </c>
+      <c r="HQ21" t="n">
+        <v/>
+      </c>
+      <c r="HR21" t="n">
+        <v/>
+      </c>
+      <c r="HS21" t="n">
+        <v/>
+      </c>
+      <c r="HT21" t="n">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -12253,9 +15388,30 @@
       <c r="C22" t="n">
         <v>-0.1055135637358951</v>
       </c>
+      <c r="D22" t="n">
+        <v/>
+      </c>
+      <c r="E22" t="n">
+        <v/>
+      </c>
+      <c r="F22" t="n">
+        <v/>
+      </c>
+      <c r="G22" t="n">
+        <v/>
+      </c>
       <c r="H22" t="n">
         <v>0.5698406001003791</v>
       </c>
+      <c r="I22" t="n">
+        <v/>
+      </c>
+      <c r="J22" t="n">
+        <v/>
+      </c>
+      <c r="K22" t="n">
+        <v/>
+      </c>
       <c r="L22" t="n">
         <v>-0.6972697602570321</v>
       </c>
@@ -12283,9 +15439,30 @@
       <c r="T22" t="n">
         <v>-0.2083909774358217</v>
       </c>
+      <c r="U22" t="n">
+        <v/>
+      </c>
+      <c r="V22" t="n">
+        <v/>
+      </c>
+      <c r="W22" t="n">
+        <v/>
+      </c>
+      <c r="X22" t="n">
+        <v/>
+      </c>
       <c r="Y22" t="n">
         <v>0.6986474362733766</v>
       </c>
+      <c r="Z22" t="n">
+        <v/>
+      </c>
+      <c r="AA22" t="n">
+        <v/>
+      </c>
+      <c r="AB22" t="n">
+        <v/>
+      </c>
       <c r="AC22" t="n">
         <v>-0.5693142915921064</v>
       </c>
@@ -12325,6 +15502,15 @@
       <c r="AO22" t="n">
         <v>0.1751077448774968</v>
       </c>
+      <c r="AP22" t="n">
+        <v/>
+      </c>
+      <c r="AQ22" t="n">
+        <v/>
+      </c>
+      <c r="AR22" t="n">
+        <v/>
+      </c>
       <c r="AS22" t="n">
         <v>-0.6972101422426633</v>
       </c>
@@ -12361,6 +15547,15 @@
       <c r="BD22" t="n">
         <v>0.8100162604832898</v>
       </c>
+      <c r="BE22" t="n">
+        <v/>
+      </c>
+      <c r="BF22" t="n">
+        <v/>
+      </c>
+      <c r="BG22" t="n">
+        <v/>
+      </c>
       <c r="BH22" t="n">
         <v>-0.3648959763055469</v>
       </c>
@@ -12394,6 +15589,15 @@
       <c r="BR22" t="n">
         <v>0.7705868077081808</v>
       </c>
+      <c r="BS22" t="n">
+        <v/>
+      </c>
+      <c r="BT22" t="n">
+        <v/>
+      </c>
+      <c r="BU22" t="n">
+        <v/>
+      </c>
       <c r="BV22" t="n">
         <v>-0.2697407415017806</v>
       </c>
@@ -12424,6 +15628,15 @@
       <c r="CE22" t="n">
         <v>0.9253347299166986</v>
       </c>
+      <c r="CF22" t="n">
+        <v/>
+      </c>
+      <c r="CG22" t="n">
+        <v/>
+      </c>
+      <c r="CH22" t="n">
+        <v/>
+      </c>
       <c r="CI22" t="n">
         <v>-0.003894094242167445</v>
       </c>
@@ -12451,6 +15664,15 @@
       <c r="CQ22" t="n">
         <v>0.823269545354622</v>
       </c>
+      <c r="CR22" t="n">
+        <v/>
+      </c>
+      <c r="CS22" t="n">
+        <v/>
+      </c>
+      <c r="CT22" t="n">
+        <v/>
+      </c>
       <c r="CU22" t="n">
         <v>-0.8607112931471302</v>
       </c>
@@ -12577,23 +15799,101 @@
       <c r="EJ22" t="n">
         <v>0.4203087804671932</v>
       </c>
+      <c r="EK22" t="n">
+        <v/>
+      </c>
+      <c r="EL22" t="n">
+        <v/>
+      </c>
+      <c r="EM22" t="n">
+        <v/>
+      </c>
+      <c r="EN22" t="n">
+        <v/>
+      </c>
+      <c r="EO22" t="n">
+        <v/>
+      </c>
       <c r="EP22" t="n">
         <v>0.6784221931074779</v>
       </c>
       <c r="EQ22" t="n">
         <v>0.7528106437943396</v>
       </c>
+      <c r="ER22" t="n">
+        <v/>
+      </c>
+      <c r="ES22" t="n">
+        <v/>
+      </c>
+      <c r="ET22" t="n">
+        <v/>
+      </c>
+      <c r="EU22" t="n">
+        <v/>
+      </c>
+      <c r="EV22" t="n">
+        <v/>
+      </c>
       <c r="EW22" t="n">
         <v>-0.2640419283244623</v>
       </c>
+      <c r="EX22" t="n">
+        <v/>
+      </c>
+      <c r="EY22" t="n">
+        <v/>
+      </c>
+      <c r="EZ22" t="n">
+        <v/>
+      </c>
+      <c r="FA22" t="n">
+        <v/>
+      </c>
+      <c r="FB22" t="n">
+        <v/>
+      </c>
+      <c r="FC22" t="n">
+        <v/>
+      </c>
+      <c r="FD22" t="n">
+        <v/>
+      </c>
+      <c r="FE22" t="n">
+        <v/>
+      </c>
+      <c r="FF22" t="n">
+        <v/>
+      </c>
+      <c r="FG22" t="n">
+        <v/>
+      </c>
       <c r="FH22" t="n">
         <v>-0.4029287761065865</v>
       </c>
       <c r="FI22" t="n">
         <v>0.04519756465222408</v>
       </c>
+      <c r="FJ22" t="n">
+        <v/>
+      </c>
+      <c r="FK22" t="n">
+        <v/>
+      </c>
       <c r="FL22" t="n">
         <v>0.6148190411542724</v>
+      </c>
+      <c r="FM22" t="n">
+        <v/>
+      </c>
+      <c r="FN22" t="n">
+        <v/>
+      </c>
+      <c r="FO22" t="n">
+        <v/>
+      </c>
+      <c r="FP22" t="n">
+        <v/>
       </c>
       <c r="FQ22" t="n">
         <v>0.08329311597780441</v>
@@ -12778,9 +16078,30 @@
       <c r="C23" t="n">
         <v>0.108608212071106</v>
       </c>
+      <c r="D23" t="n">
+        <v/>
+      </c>
+      <c r="E23" t="n">
+        <v/>
+      </c>
+      <c r="F23" t="n">
+        <v/>
+      </c>
+      <c r="G23" t="n">
+        <v/>
+      </c>
       <c r="H23" t="n">
         <v>0.8197232643123288</v>
       </c>
+      <c r="I23" t="n">
+        <v/>
+      </c>
+      <c r="J23" t="n">
+        <v/>
+      </c>
+      <c r="K23" t="n">
+        <v/>
+      </c>
       <c r="L23" t="n">
         <v>-0.48883508382879</v>
       </c>
@@ -12808,9 +16129,30 @@
       <c r="T23" t="n">
         <v>-0.8102800780070375</v>
       </c>
+      <c r="U23" t="n">
+        <v/>
+      </c>
+      <c r="V23" t="n">
+        <v/>
+      </c>
+      <c r="W23" t="n">
+        <v/>
+      </c>
+      <c r="X23" t="n">
+        <v/>
+      </c>
       <c r="Y23" t="n">
         <v>0.8386356117539545</v>
       </c>
+      <c r="Z23" t="n">
+        <v/>
+      </c>
+      <c r="AA23" t="n">
+        <v/>
+      </c>
+      <c r="AB23" t="n">
+        <v/>
+      </c>
       <c r="AC23" t="n">
         <v>-0.4318257890059532</v>
       </c>
@@ -12850,6 +16192,15 @@
       <c r="AO23" t="n">
         <v>0.3012788418774329</v>
       </c>
+      <c r="AP23" t="n">
+        <v/>
+      </c>
+      <c r="AQ23" t="n">
+        <v/>
+      </c>
+      <c r="AR23" t="n">
+        <v/>
+      </c>
       <c r="AS23" t="n">
         <v>-0.9240054537420764</v>
       </c>
@@ -12886,6 +16237,15 @@
       <c r="BD23" t="n">
         <v>0.7870331542205945</v>
       </c>
+      <c r="BE23" t="n">
+        <v/>
+      </c>
+      <c r="BF23" t="n">
+        <v/>
+      </c>
+      <c r="BG23" t="n">
+        <v/>
+      </c>
       <c r="BH23" t="n">
         <v>-0.7833001657981193</v>
       </c>
@@ -12919,6 +16279,15 @@
       <c r="BR23" t="n">
         <v>0.6540678712384909</v>
       </c>
+      <c r="BS23" t="n">
+        <v/>
+      </c>
+      <c r="BT23" t="n">
+        <v/>
+      </c>
+      <c r="BU23" t="n">
+        <v/>
+      </c>
       <c r="BV23" t="n">
         <v>-0.5311275820319926</v>
       </c>
@@ -12949,6 +16318,15 @@
       <c r="CE23" t="n">
         <v>0.819227774831892</v>
       </c>
+      <c r="CF23" t="n">
+        <v/>
+      </c>
+      <c r="CG23" t="n">
+        <v/>
+      </c>
+      <c r="CH23" t="n">
+        <v/>
+      </c>
       <c r="CI23" t="n">
         <v>-0.4361441534932132</v>
       </c>
@@ -12976,6 +16354,15 @@
       <c r="CQ23" t="n">
         <v>-0.8681313828717544</v>
       </c>
+      <c r="CR23" t="n">
+        <v/>
+      </c>
+      <c r="CS23" t="n">
+        <v/>
+      </c>
+      <c r="CT23" t="n">
+        <v/>
+      </c>
       <c r="CU23" t="n">
         <v>-0.8064940455187546</v>
       </c>
@@ -13102,23 +16489,101 @@
       <c r="EJ23" t="n">
         <v>0.1488270800022868</v>
       </c>
+      <c r="EK23" t="n">
+        <v/>
+      </c>
+      <c r="EL23" t="n">
+        <v/>
+      </c>
+      <c r="EM23" t="n">
+        <v/>
+      </c>
+      <c r="EN23" t="n">
+        <v/>
+      </c>
+      <c r="EO23" t="n">
+        <v/>
+      </c>
       <c r="EP23" t="n">
         <v>0.525859622124129</v>
       </c>
       <c r="EQ23" t="n">
         <v>0.6336578980588679</v>
       </c>
+      <c r="ER23" t="n">
+        <v/>
+      </c>
+      <c r="ES23" t="n">
+        <v/>
+      </c>
+      <c r="ET23" t="n">
+        <v/>
+      </c>
+      <c r="EU23" t="n">
+        <v/>
+      </c>
+      <c r="EV23" t="n">
+        <v/>
+      </c>
       <c r="EW23" t="n">
         <v>-0.1085017825361708</v>
       </c>
+      <c r="EX23" t="n">
+        <v/>
+      </c>
+      <c r="EY23" t="n">
+        <v/>
+      </c>
+      <c r="EZ23" t="n">
+        <v/>
+      </c>
+      <c r="FA23" t="n">
+        <v/>
+      </c>
+      <c r="FB23" t="n">
+        <v/>
+      </c>
+      <c r="FC23" t="n">
+        <v/>
+      </c>
+      <c r="FD23" t="n">
+        <v/>
+      </c>
+      <c r="FE23" t="n">
+        <v/>
+      </c>
+      <c r="FF23" t="n">
+        <v/>
+      </c>
+      <c r="FG23" t="n">
+        <v/>
+      </c>
       <c r="FH23" t="n">
         <v>-0.05941805695301304</v>
       </c>
       <c r="FI23" t="n">
         <v>-0.4673691544237483</v>
       </c>
+      <c r="FJ23" t="n">
+        <v/>
+      </c>
+      <c r="FK23" t="n">
+        <v/>
+      </c>
       <c r="FL23" t="n">
         <v>-0.271161063739926</v>
+      </c>
+      <c r="FM23" t="n">
+        <v/>
+      </c>
+      <c r="FN23" t="n">
+        <v/>
+      </c>
+      <c r="FO23" t="n">
+        <v/>
+      </c>
+      <c r="FP23" t="n">
+        <v/>
       </c>
       <c r="FQ23" t="n">
         <v>-0.9573541186840414</v>
@@ -13303,9 +16768,30 @@
       <c r="C24" t="n">
         <v>-0.2793519750164083</v>
       </c>
+      <c r="D24" t="n">
+        <v/>
+      </c>
+      <c r="E24" t="n">
+        <v/>
+      </c>
+      <c r="F24" t="n">
+        <v/>
+      </c>
+      <c r="G24" t="n">
+        <v/>
+      </c>
       <c r="H24" t="n">
         <v>0.7440996435223393</v>
       </c>
+      <c r="I24" t="n">
+        <v/>
+      </c>
+      <c r="J24" t="n">
+        <v/>
+      </c>
+      <c r="K24" t="n">
+        <v/>
+      </c>
       <c r="L24" t="n">
         <v>-0.3093981804323638</v>
       </c>
@@ -13333,9 +16819,30 @@
       <c r="T24" t="n">
         <v>-0.3135746060974476</v>
       </c>
+      <c r="U24" t="n">
+        <v/>
+      </c>
+      <c r="V24" t="n">
+        <v/>
+      </c>
+      <c r="W24" t="n">
+        <v/>
+      </c>
+      <c r="X24" t="n">
+        <v/>
+      </c>
       <c r="Y24" t="n">
         <v>0.7132971007603526</v>
       </c>
+      <c r="Z24" t="n">
+        <v/>
+      </c>
+      <c r="AA24" t="n">
+        <v/>
+      </c>
+      <c r="AB24" t="n">
+        <v/>
+      </c>
       <c r="AC24" t="n">
         <v>-0.2172109508405989</v>
       </c>
@@ -13375,6 +16882,15 @@
       <c r="AO24" t="n">
         <v>0.8362713022258175</v>
       </c>
+      <c r="AP24" t="n">
+        <v/>
+      </c>
+      <c r="AQ24" t="n">
+        <v/>
+      </c>
+      <c r="AR24" t="n">
+        <v/>
+      </c>
       <c r="AS24" t="n">
         <v>-0.1079765864441441</v>
       </c>
@@ -13411,6 +16927,15 @@
       <c r="BD24" t="n">
         <v>0.5916197059760979</v>
       </c>
+      <c r="BE24" t="n">
+        <v/>
+      </c>
+      <c r="BF24" t="n">
+        <v/>
+      </c>
+      <c r="BG24" t="n">
+        <v/>
+      </c>
       <c r="BH24" t="n">
         <v>-0.4807289191252312</v>
       </c>
@@ -13444,6 +16969,15 @@
       <c r="BR24" t="n">
         <v>0.7917499512354177</v>
       </c>
+      <c r="BS24" t="n">
+        <v/>
+      </c>
+      <c r="BT24" t="n">
+        <v/>
+      </c>
+      <c r="BU24" t="n">
+        <v/>
+      </c>
       <c r="BV24" t="n">
         <v>-0.5165574846375264</v>
       </c>
@@ -13474,6 +17008,15 @@
       <c r="CE24" t="n">
         <v>0.5627291126180186</v>
       </c>
+      <c r="CF24" t="n">
+        <v/>
+      </c>
+      <c r="CG24" t="n">
+        <v/>
+      </c>
+      <c r="CH24" t="n">
+        <v/>
+      </c>
       <c r="CI24" t="n">
         <v>-0.733774825956504</v>
       </c>
@@ -13501,6 +17044,15 @@
       <c r="CQ24" t="n">
         <v>-0.4011839687633341</v>
       </c>
+      <c r="CR24" t="n">
+        <v/>
+      </c>
+      <c r="CS24" t="n">
+        <v/>
+      </c>
+      <c r="CT24" t="n">
+        <v/>
+      </c>
       <c r="CU24" t="n">
         <v>-0.8234840518187507</v>
       </c>
@@ -13627,23 +17179,101 @@
       <c r="EJ24" t="n">
         <v>0.4986274762128197</v>
       </c>
+      <c r="EK24" t="n">
+        <v/>
+      </c>
+      <c r="EL24" t="n">
+        <v/>
+      </c>
+      <c r="EM24" t="n">
+        <v/>
+      </c>
+      <c r="EN24" t="n">
+        <v/>
+      </c>
+      <c r="EO24" t="n">
+        <v/>
+      </c>
       <c r="EP24" t="n">
         <v>0.7452518055667336</v>
       </c>
       <c r="EQ24" t="n">
         <v>0.8049318355558963</v>
       </c>
+      <c r="ER24" t="n">
+        <v/>
+      </c>
+      <c r="ES24" t="n">
+        <v/>
+      </c>
+      <c r="ET24" t="n">
+        <v/>
+      </c>
+      <c r="EU24" t="n">
+        <v/>
+      </c>
+      <c r="EV24" t="n">
+        <v/>
+      </c>
       <c r="EW24" t="n">
         <v>-0.05386151407355012</v>
       </c>
+      <c r="EX24" t="n">
+        <v/>
+      </c>
+      <c r="EY24" t="n">
+        <v/>
+      </c>
+      <c r="EZ24" t="n">
+        <v/>
+      </c>
+      <c r="FA24" t="n">
+        <v/>
+      </c>
+      <c r="FB24" t="n">
+        <v/>
+      </c>
+      <c r="FC24" t="n">
+        <v/>
+      </c>
+      <c r="FD24" t="n">
+        <v/>
+      </c>
+      <c r="FE24" t="n">
+        <v/>
+      </c>
+      <c r="FF24" t="n">
+        <v/>
+      </c>
+      <c r="FG24" t="n">
+        <v/>
+      </c>
       <c r="FH24" t="n">
         <v>0.2967754226443652</v>
       </c>
       <c r="FI24" t="n">
         <v>0.2463754511906179</v>
       </c>
+      <c r="FJ24" t="n">
+        <v/>
+      </c>
+      <c r="FK24" t="n">
+        <v/>
+      </c>
       <c r="FL24" t="n">
         <v>0.1157465309069195</v>
+      </c>
+      <c r="FM24" t="n">
+        <v/>
+      </c>
+      <c r="FN24" t="n">
+        <v/>
+      </c>
+      <c r="FO24" t="n">
+        <v/>
+      </c>
+      <c r="FP24" t="n">
+        <v/>
       </c>
       <c r="FQ24" t="n">
         <v>-0.6671459499620467</v>
@@ -13828,9 +17458,30 @@
       <c r="C25" t="n">
         <v>0.2953312461064304</v>
       </c>
+      <c r="D25" t="n">
+        <v/>
+      </c>
+      <c r="E25" t="n">
+        <v/>
+      </c>
+      <c r="F25" t="n">
+        <v/>
+      </c>
+      <c r="G25" t="n">
+        <v/>
+      </c>
       <c r="H25" t="n">
         <v>0.6846250825145035</v>
       </c>
+      <c r="I25" t="n">
+        <v/>
+      </c>
+      <c r="J25" t="n">
+        <v/>
+      </c>
+      <c r="K25" t="n">
+        <v/>
+      </c>
       <c r="L25" t="n">
         <v>0.1126945625550382</v>
       </c>
@@ -13858,9 +17509,30 @@
       <c r="T25" t="n">
         <v>-0.4330823377274949</v>
       </c>
+      <c r="U25" t="n">
+        <v/>
+      </c>
+      <c r="V25" t="n">
+        <v/>
+      </c>
+      <c r="W25" t="n">
+        <v/>
+      </c>
+      <c r="X25" t="n">
+        <v/>
+      </c>
       <c r="Y25" t="n">
         <v>0.5848838026860401</v>
       </c>
+      <c r="Z25" t="n">
+        <v/>
+      </c>
+      <c r="AA25" t="n">
+        <v/>
+      </c>
+      <c r="AB25" t="n">
+        <v/>
+      </c>
       <c r="AC25" t="n">
         <v>0.006952388970446069</v>
       </c>
@@ -13900,6 +17572,15 @@
       <c r="AO25" t="n">
         <v>0.6759933941512773</v>
       </c>
+      <c r="AP25" t="n">
+        <v/>
+      </c>
+      <c r="AQ25" t="n">
+        <v/>
+      </c>
+      <c r="AR25" t="n">
+        <v/>
+      </c>
       <c r="AS25" t="n">
         <v>0.08444776390023705</v>
       </c>
@@ -13936,6 +17617,15 @@
       <c r="BD25" t="n">
         <v>0.5350829385534218</v>
       </c>
+      <c r="BE25" t="n">
+        <v/>
+      </c>
+      <c r="BF25" t="n">
+        <v/>
+      </c>
+      <c r="BG25" t="n">
+        <v/>
+      </c>
       <c r="BH25" t="n">
         <v>-0.1321187558972146</v>
       </c>
@@ -13969,6 +17659,15 @@
       <c r="BR25" t="n">
         <v>0.5078258782029417</v>
       </c>
+      <c r="BS25" t="n">
+        <v/>
+      </c>
+      <c r="BT25" t="n">
+        <v/>
+      </c>
+      <c r="BU25" t="n">
+        <v/>
+      </c>
       <c r="BV25" t="n">
         <v>0.003254000322052986</v>
       </c>
@@ -13999,6 +17698,15 @@
       <c r="CE25" t="n">
         <v>0.3791661615009845</v>
       </c>
+      <c r="CF25" t="n">
+        <v/>
+      </c>
+      <c r="CG25" t="n">
+        <v/>
+      </c>
+      <c r="CH25" t="n">
+        <v/>
+      </c>
       <c r="CI25" t="n">
         <v>-0.121897601651218</v>
       </c>
@@ -14026,6 +17734,15 @@
       <c r="CQ25" t="n">
         <v>-0.4674104795929694</v>
       </c>
+      <c r="CR25" t="n">
+        <v/>
+      </c>
+      <c r="CS25" t="n">
+        <v/>
+      </c>
+      <c r="CT25" t="n">
+        <v/>
+      </c>
       <c r="CU25" t="n">
         <v>-0.444837883136035</v>
       </c>
@@ -14152,23 +17869,101 @@
       <c r="EJ25" t="n">
         <v>0.5970753931775344</v>
       </c>
+      <c r="EK25" t="n">
+        <v/>
+      </c>
+      <c r="EL25" t="n">
+        <v/>
+      </c>
+      <c r="EM25" t="n">
+        <v/>
+      </c>
+      <c r="EN25" t="n">
+        <v/>
+      </c>
+      <c r="EO25" t="n">
+        <v/>
+      </c>
       <c r="EP25" t="n">
         <v>0.4192873973451594</v>
       </c>
       <c r="EQ25" t="n">
         <v>0.6421559503173723</v>
       </c>
+      <c r="ER25" t="n">
+        <v/>
+      </c>
+      <c r="ES25" t="n">
+        <v/>
+      </c>
+      <c r="ET25" t="n">
+        <v/>
+      </c>
+      <c r="EU25" t="n">
+        <v/>
+      </c>
+      <c r="EV25" t="n">
+        <v/>
+      </c>
       <c r="EW25" t="n">
         <v>-0.06330594566576905</v>
       </c>
+      <c r="EX25" t="n">
+        <v/>
+      </c>
+      <c r="EY25" t="n">
+        <v/>
+      </c>
+      <c r="EZ25" t="n">
+        <v/>
+      </c>
+      <c r="FA25" t="n">
+        <v/>
+      </c>
+      <c r="FB25" t="n">
+        <v/>
+      </c>
+      <c r="FC25" t="n">
+        <v/>
+      </c>
+      <c r="FD25" t="n">
+        <v/>
+      </c>
+      <c r="FE25" t="n">
+        <v/>
+      </c>
+      <c r="FF25" t="n">
+        <v/>
+      </c>
+      <c r="FG25" t="n">
+        <v/>
+      </c>
       <c r="FH25" t="n">
         <v>0.1620553954788408</v>
       </c>
       <c r="FI25" t="n">
         <v>0.1543853312347571</v>
       </c>
+      <c r="FJ25" t="n">
+        <v/>
+      </c>
+      <c r="FK25" t="n">
+        <v/>
+      </c>
       <c r="FL25" t="n">
         <v>0.03887232792169378</v>
+      </c>
+      <c r="FM25" t="n">
+        <v/>
+      </c>
+      <c r="FN25" t="n">
+        <v/>
+      </c>
+      <c r="FO25" t="n">
+        <v/>
+      </c>
+      <c r="FP25" t="n">
+        <v/>
       </c>
       <c r="FQ25" t="n">
         <v>-0.64359949140997</v>
@@ -14353,9 +18148,30 @@
       <c r="C26" t="n">
         <v>0.1965960448702238</v>
       </c>
+      <c r="D26" t="n">
+        <v/>
+      </c>
+      <c r="E26" t="n">
+        <v/>
+      </c>
+      <c r="F26" t="n">
+        <v/>
+      </c>
+      <c r="G26" t="n">
+        <v/>
+      </c>
       <c r="H26" t="n">
         <v>0.4910746351557049</v>
       </c>
+      <c r="I26" t="n">
+        <v/>
+      </c>
+      <c r="J26" t="n">
+        <v/>
+      </c>
+      <c r="K26" t="n">
+        <v/>
+      </c>
       <c r="L26" t="n">
         <v>-0.4766204813322876</v>
       </c>
@@ -14383,9 +18199,30 @@
       <c r="T26" t="n">
         <v>-0.3047285853454712</v>
       </c>
+      <c r="U26" t="n">
+        <v/>
+      </c>
+      <c r="V26" t="n">
+        <v/>
+      </c>
+      <c r="W26" t="n">
+        <v/>
+      </c>
+      <c r="X26" t="n">
+        <v/>
+      </c>
       <c r="Y26" t="n">
         <v>0.43166765796435</v>
       </c>
+      <c r="Z26" t="n">
+        <v/>
+      </c>
+      <c r="AA26" t="n">
+        <v/>
+      </c>
+      <c r="AB26" t="n">
+        <v/>
+      </c>
       <c r="AC26" t="n">
         <v>-0.5227770598149675</v>
       </c>
@@ -14425,6 +18262,15 @@
       <c r="AO26" t="n">
         <v>0.4485270939594474</v>
       </c>
+      <c r="AP26" t="n">
+        <v/>
+      </c>
+      <c r="AQ26" t="n">
+        <v/>
+      </c>
+      <c r="AR26" t="n">
+        <v/>
+      </c>
       <c r="AS26" t="n">
         <v>-0.07089978160391422</v>
       </c>
@@ -14461,6 +18307,15 @@
       <c r="BD26" t="n">
         <v>0.4108623601376678</v>
       </c>
+      <c r="BE26" t="n">
+        <v/>
+      </c>
+      <c r="BF26" t="n">
+        <v/>
+      </c>
+      <c r="BG26" t="n">
+        <v/>
+      </c>
       <c r="BH26" t="n">
         <v>-0.2537247516231785</v>
       </c>
@@ -14494,6 +18349,15 @@
       <c r="BR26" t="n">
         <v>0.478510536208727</v>
       </c>
+      <c r="BS26" t="n">
+        <v/>
+      </c>
+      <c r="BT26" t="n">
+        <v/>
+      </c>
+      <c r="BU26" t="n">
+        <v/>
+      </c>
       <c r="BV26" t="n">
         <v>-0.3777950563566662</v>
       </c>
@@ -14524,6 +18388,15 @@
       <c r="CE26" t="n">
         <v>0.3517390083362885</v>
       </c>
+      <c r="CF26" t="n">
+        <v/>
+      </c>
+      <c r="CG26" t="n">
+        <v/>
+      </c>
+      <c r="CH26" t="n">
+        <v/>
+      </c>
       <c r="CI26" t="n">
         <v>-0.3408038180044845</v>
       </c>
@@ -14551,6 +18424,15 @@
       <c r="CQ26" t="n">
         <v>0.1968064187404623</v>
       </c>
+      <c r="CR26" t="n">
+        <v/>
+      </c>
+      <c r="CS26" t="n">
+        <v/>
+      </c>
+      <c r="CT26" t="n">
+        <v/>
+      </c>
       <c r="CU26" t="n">
         <v>-0.6078091192766939</v>
       </c>
@@ -14677,23 +18559,101 @@
       <c r="EJ26" t="n">
         <v>0.03376374881502753</v>
       </c>
+      <c r="EK26" t="n">
+        <v/>
+      </c>
+      <c r="EL26" t="n">
+        <v/>
+      </c>
+      <c r="EM26" t="n">
+        <v/>
+      </c>
+      <c r="EN26" t="n">
+        <v/>
+      </c>
+      <c r="EO26" t="n">
+        <v/>
+      </c>
       <c r="EP26" t="n">
         <v>0.1797536877542573</v>
       </c>
       <c r="EQ26" t="n">
         <v>0.0813667475515325</v>
       </c>
+      <c r="ER26" t="n">
+        <v/>
+      </c>
+      <c r="ES26" t="n">
+        <v/>
+      </c>
+      <c r="ET26" t="n">
+        <v/>
+      </c>
+      <c r="EU26" t="n">
+        <v/>
+      </c>
+      <c r="EV26" t="n">
+        <v/>
+      </c>
       <c r="EW26" t="n">
         <v>-0.2817118747694944</v>
       </c>
+      <c r="EX26" t="n">
+        <v/>
+      </c>
+      <c r="EY26" t="n">
+        <v/>
+      </c>
+      <c r="EZ26" t="n">
+        <v/>
+      </c>
+      <c r="FA26" t="n">
+        <v/>
+      </c>
+      <c r="FB26" t="n">
+        <v/>
+      </c>
+      <c r="FC26" t="n">
+        <v/>
+      </c>
+      <c r="FD26" t="n">
+        <v/>
+      </c>
+      <c r="FE26" t="n">
+        <v/>
+      </c>
+      <c r="FF26" t="n">
+        <v/>
+      </c>
+      <c r="FG26" t="n">
+        <v/>
+      </c>
       <c r="FH26" t="n">
         <v>0.225272697983396</v>
       </c>
       <c r="FI26" t="n">
         <v>0.4978883966172735</v>
       </c>
+      <c r="FJ26" t="n">
+        <v/>
+      </c>
+      <c r="FK26" t="n">
+        <v/>
+      </c>
       <c r="FL26" t="n">
         <v>0.1607986774190703</v>
+      </c>
+      <c r="FM26" t="n">
+        <v/>
+      </c>
+      <c r="FN26" t="n">
+        <v/>
+      </c>
+      <c r="FO26" t="n">
+        <v/>
+      </c>
+      <c r="FP26" t="n">
+        <v/>
       </c>
       <c r="FQ26" t="n">
         <v>0.5346125919512106</v>
@@ -14878,9 +18838,30 @@
       <c r="C27" t="n">
         <v>0.3992465070248511</v>
       </c>
+      <c r="D27" t="n">
+        <v/>
+      </c>
+      <c r="E27" t="n">
+        <v/>
+      </c>
+      <c r="F27" t="n">
+        <v/>
+      </c>
+      <c r="G27" t="n">
+        <v/>
+      </c>
       <c r="H27" t="n">
         <v>0.8996842400719768</v>
       </c>
+      <c r="I27" t="n">
+        <v/>
+      </c>
+      <c r="J27" t="n">
+        <v/>
+      </c>
+      <c r="K27" t="n">
+        <v/>
+      </c>
       <c r="L27" t="n">
         <v>-0.2341400325859441</v>
       </c>
@@ -14908,9 +18889,30 @@
       <c r="T27" t="n">
         <v>0.6962712370306299</v>
       </c>
+      <c r="U27" t="n">
+        <v/>
+      </c>
+      <c r="V27" t="n">
+        <v/>
+      </c>
+      <c r="W27" t="n">
+        <v/>
+      </c>
+      <c r="X27" t="n">
+        <v/>
+      </c>
       <c r="Y27" t="n">
         <v>0.8611848932271091</v>
       </c>
+      <c r="Z27" t="n">
+        <v/>
+      </c>
+      <c r="AA27" t="n">
+        <v/>
+      </c>
+      <c r="AB27" t="n">
+        <v/>
+      </c>
       <c r="AC27" t="n">
         <v>-0.5815620139772943</v>
       </c>
@@ -14950,6 +18952,15 @@
       <c r="AO27" t="n">
         <v>0.4241980080861404</v>
       </c>
+      <c r="AP27" t="n">
+        <v/>
+      </c>
+      <c r="AQ27" t="n">
+        <v/>
+      </c>
+      <c r="AR27" t="n">
+        <v/>
+      </c>
       <c r="AS27" t="n">
         <v>-0.8983401877311877</v>
       </c>
@@ -14986,6 +18997,15 @@
       <c r="BD27" t="n">
         <v>0.8375635276216011</v>
       </c>
+      <c r="BE27" t="n">
+        <v/>
+      </c>
+      <c r="BF27" t="n">
+        <v/>
+      </c>
+      <c r="BG27" t="n">
+        <v/>
+      </c>
       <c r="BH27" t="n">
         <v>-0.7670133941534181</v>
       </c>
@@ -15019,6 +19039,15 @@
       <c r="BR27" t="n">
         <v>0.8994433099722248</v>
       </c>
+      <c r="BS27" t="n">
+        <v/>
+      </c>
+      <c r="BT27" t="n">
+        <v/>
+      </c>
+      <c r="BU27" t="n">
+        <v/>
+      </c>
       <c r="BV27" t="n">
         <v>-0.3460153533357089</v>
       </c>
@@ -15049,6 +19078,15 @@
       <c r="CE27" t="n">
         <v>0.865857106810008</v>
       </c>
+      <c r="CF27" t="n">
+        <v/>
+      </c>
+      <c r="CG27" t="n">
+        <v/>
+      </c>
+      <c r="CH27" t="n">
+        <v/>
+      </c>
       <c r="CI27" t="n">
         <v>-0.3870098177567938</v>
       </c>
@@ -15076,6 +19114,15 @@
       <c r="CQ27" t="n">
         <v>0.8102564028298586</v>
       </c>
+      <c r="CR27" t="n">
+        <v/>
+      </c>
+      <c r="CS27" t="n">
+        <v/>
+      </c>
+      <c r="CT27" t="n">
+        <v/>
+      </c>
       <c r="CU27" t="n">
         <v>-0.9328350503839868</v>
       </c>
@@ -15202,23 +19249,101 @@
       <c r="EJ27" t="n">
         <v>0.7720070351194149</v>
       </c>
+      <c r="EK27" t="n">
+        <v/>
+      </c>
+      <c r="EL27" t="n">
+        <v/>
+      </c>
+      <c r="EM27" t="n">
+        <v/>
+      </c>
+      <c r="EN27" t="n">
+        <v/>
+      </c>
+      <c r="EO27" t="n">
+        <v/>
+      </c>
       <c r="EP27" t="n">
         <v>-0.3216398016793401</v>
       </c>
       <c r="EQ27" t="n">
         <v>0.6441727581342567</v>
       </c>
+      <c r="ER27" t="n">
+        <v/>
+      </c>
+      <c r="ES27" t="n">
+        <v/>
+      </c>
+      <c r="ET27" t="n">
+        <v/>
+      </c>
+      <c r="EU27" t="n">
+        <v/>
+      </c>
+      <c r="EV27" t="n">
+        <v/>
+      </c>
       <c r="EW27" t="n">
         <v>0.6597465035337041</v>
       </c>
+      <c r="EX27" t="n">
+        <v/>
+      </c>
+      <c r="EY27" t="n">
+        <v/>
+      </c>
+      <c r="EZ27" t="n">
+        <v/>
+      </c>
+      <c r="FA27" t="n">
+        <v/>
+      </c>
+      <c r="FB27" t="n">
+        <v/>
+      </c>
+      <c r="FC27" t="n">
+        <v/>
+      </c>
+      <c r="FD27" t="n">
+        <v/>
+      </c>
+      <c r="FE27" t="n">
+        <v/>
+      </c>
+      <c r="FF27" t="n">
+        <v/>
+      </c>
+      <c r="FG27" t="n">
+        <v/>
+      </c>
       <c r="FH27" t="n">
         <v>-0.3663866632421985</v>
       </c>
       <c r="FI27" t="n">
         <v>-0.1754654184884691</v>
       </c>
+      <c r="FJ27" t="n">
+        <v/>
+      </c>
+      <c r="FK27" t="n">
+        <v/>
+      </c>
       <c r="FL27" t="n">
         <v>0.4464451098568449</v>
+      </c>
+      <c r="FM27" t="n">
+        <v/>
+      </c>
+      <c r="FN27" t="n">
+        <v/>
+      </c>
+      <c r="FO27" t="n">
+        <v/>
+      </c>
+      <c r="FP27" t="n">
+        <v/>
       </c>
       <c r="FQ27" t="n">
         <v>0.6391723095351809</v>
@@ -15403,9 +19528,30 @@
       <c r="C28" t="n">
         <v>0.1530639760910168</v>
       </c>
+      <c r="D28" t="n">
+        <v/>
+      </c>
+      <c r="E28" t="n">
+        <v/>
+      </c>
+      <c r="F28" t="n">
+        <v/>
+      </c>
+      <c r="G28" t="n">
+        <v/>
+      </c>
       <c r="H28" t="n">
         <v>0.8884298084842305</v>
       </c>
+      <c r="I28" t="n">
+        <v/>
+      </c>
+      <c r="J28" t="n">
+        <v/>
+      </c>
+      <c r="K28" t="n">
+        <v/>
+      </c>
       <c r="L28" t="n">
         <v>0.2312021303144434</v>
       </c>
@@ -15433,9 +19579,30 @@
       <c r="T28" t="n">
         <v>0.8528148558835115</v>
       </c>
+      <c r="U28" t="n">
+        <v/>
+      </c>
+      <c r="V28" t="n">
+        <v/>
+      </c>
+      <c r="W28" t="n">
+        <v/>
+      </c>
+      <c r="X28" t="n">
+        <v/>
+      </c>
       <c r="Y28" t="n">
         <v>0.8209131728280393</v>
       </c>
+      <c r="Z28" t="n">
+        <v/>
+      </c>
+      <c r="AA28" t="n">
+        <v/>
+      </c>
+      <c r="AB28" t="n">
+        <v/>
+      </c>
       <c r="AC28" t="n">
         <v>0.0622257951342315</v>
       </c>
@@ -15475,6 +19642,15 @@
       <c r="AO28" t="n">
         <v>0.389640534395951</v>
       </c>
+      <c r="AP28" t="n">
+        <v/>
+      </c>
+      <c r="AQ28" t="n">
+        <v/>
+      </c>
+      <c r="AR28" t="n">
+        <v/>
+      </c>
       <c r="AS28" t="n">
         <v>-0.7353697992008577</v>
       </c>
@@ -15511,6 +19687,15 @@
       <c r="BD28" t="n">
         <v>0.5541935644186913</v>
       </c>
+      <c r="BE28" t="n">
+        <v/>
+      </c>
+      <c r="BF28" t="n">
+        <v/>
+      </c>
+      <c r="BG28" t="n">
+        <v/>
+      </c>
       <c r="BH28" t="n">
         <v>-0.6517965840926111</v>
       </c>
@@ -15544,6 +19729,15 @@
       <c r="BR28" t="n">
         <v>0.8656546677827451</v>
       </c>
+      <c r="BS28" t="n">
+        <v/>
+      </c>
+      <c r="BT28" t="n">
+        <v/>
+      </c>
+      <c r="BU28" t="n">
+        <v/>
+      </c>
       <c r="BV28" t="n">
         <v>-0.07184010940593186</v>
       </c>
@@ -15574,6 +19768,15 @@
       <c r="CE28" t="n">
         <v>0.9119927771147575</v>
       </c>
+      <c r="CF28" t="n">
+        <v/>
+      </c>
+      <c r="CG28" t="n">
+        <v/>
+      </c>
+      <c r="CH28" t="n">
+        <v/>
+      </c>
       <c r="CI28" t="n">
         <v>0.02617853867685049</v>
       </c>
@@ -15601,6 +19804,15 @@
       <c r="CQ28" t="n">
         <v>0.8590500117249462</v>
       </c>
+      <c r="CR28" t="n">
+        <v/>
+      </c>
+      <c r="CS28" t="n">
+        <v/>
+      </c>
+      <c r="CT28" t="n">
+        <v/>
+      </c>
       <c r="CU28" t="n">
         <v>-0.833965615636461</v>
       </c>
@@ -15727,23 +19939,101 @@
       <c r="EJ28" t="n">
         <v>0.8378386407388485</v>
       </c>
+      <c r="EK28" t="n">
+        <v/>
+      </c>
+      <c r="EL28" t="n">
+        <v/>
+      </c>
+      <c r="EM28" t="n">
+        <v/>
+      </c>
+      <c r="EN28" t="n">
+        <v/>
+      </c>
+      <c r="EO28" t="n">
+        <v/>
+      </c>
       <c r="EP28" t="n">
         <v>0.8824928571361893</v>
       </c>
       <c r="EQ28" t="n">
         <v>0.9050886992804736</v>
       </c>
+      <c r="ER28" t="n">
+        <v/>
+      </c>
+      <c r="ES28" t="n">
+        <v/>
+      </c>
+      <c r="ET28" t="n">
+        <v/>
+      </c>
+      <c r="EU28" t="n">
+        <v/>
+      </c>
+      <c r="EV28" t="n">
+        <v/>
+      </c>
       <c r="EW28" t="n">
         <v>0.05208030117720747</v>
       </c>
+      <c r="EX28" t="n">
+        <v/>
+      </c>
+      <c r="EY28" t="n">
+        <v/>
+      </c>
+      <c r="EZ28" t="n">
+        <v/>
+      </c>
+      <c r="FA28" t="n">
+        <v/>
+      </c>
+      <c r="FB28" t="n">
+        <v/>
+      </c>
+      <c r="FC28" t="n">
+        <v/>
+      </c>
+      <c r="FD28" t="n">
+        <v/>
+      </c>
+      <c r="FE28" t="n">
+        <v/>
+      </c>
+      <c r="FF28" t="n">
+        <v/>
+      </c>
+      <c r="FG28" t="n">
+        <v/>
+      </c>
       <c r="FH28" t="n">
         <v>-0.6012604748967643</v>
       </c>
       <c r="FI28" t="n">
         <v>-0.2620417789897164</v>
       </c>
+      <c r="FJ28" t="n">
+        <v/>
+      </c>
+      <c r="FK28" t="n">
+        <v/>
+      </c>
       <c r="FL28" t="n">
         <v>0.6261500209911729</v>
+      </c>
+      <c r="FM28" t="n">
+        <v/>
+      </c>
+      <c r="FN28" t="n">
+        <v/>
+      </c>
+      <c r="FO28" t="n">
+        <v/>
+      </c>
+      <c r="FP28" t="n">
+        <v/>
       </c>
       <c r="FQ28" t="n">
         <v>-0.2445819645580186</v>
@@ -15928,9 +20218,30 @@
       <c r="C29" t="n">
         <v>-0.128349989174157</v>
       </c>
+      <c r="D29" t="n">
+        <v/>
+      </c>
+      <c r="E29" t="n">
+        <v/>
+      </c>
+      <c r="F29" t="n">
+        <v/>
+      </c>
+      <c r="G29" t="n">
+        <v/>
+      </c>
       <c r="H29" t="n">
         <v>0.3856002894398106</v>
       </c>
+      <c r="I29" t="n">
+        <v/>
+      </c>
+      <c r="J29" t="n">
+        <v/>
+      </c>
+      <c r="K29" t="n">
+        <v/>
+      </c>
       <c r="L29" t="n">
         <v>-0.7668254667474357</v>
       </c>
@@ -15958,9 +20269,30 @@
       <c r="T29" t="n">
         <v>-0.693304587531413</v>
       </c>
+      <c r="U29" t="n">
+        <v/>
+      </c>
+      <c r="V29" t="n">
+        <v/>
+      </c>
+      <c r="W29" t="n">
+        <v/>
+      </c>
+      <c r="X29" t="n">
+        <v/>
+      </c>
       <c r="Y29" t="n">
         <v>0.48233003011756</v>
       </c>
+      <c r="Z29" t="n">
+        <v/>
+      </c>
+      <c r="AA29" t="n">
+        <v/>
+      </c>
+      <c r="AB29" t="n">
+        <v/>
+      </c>
       <c r="AC29" t="n">
         <v>-0.8412009892897885</v>
       </c>
@@ -16000,6 +20332,15 @@
       <c r="AO29" t="n">
         <v>0.3802942382767348</v>
       </c>
+      <c r="AP29" t="n">
+        <v/>
+      </c>
+      <c r="AQ29" t="n">
+        <v/>
+      </c>
+      <c r="AR29" t="n">
+        <v/>
+      </c>
       <c r="AS29" t="n">
         <v>-0.9430209786892663</v>
       </c>
@@ -16036,6 +20377,15 @@
       <c r="BD29" t="n">
         <v>0.6634521089666812</v>
       </c>
+      <c r="BE29" t="n">
+        <v/>
+      </c>
+      <c r="BF29" t="n">
+        <v/>
+      </c>
+      <c r="BG29" t="n">
+        <v/>
+      </c>
       <c r="BH29" t="n">
         <v>-0.7871260912629621</v>
       </c>
@@ -16069,6 +20419,15 @@
       <c r="BR29" t="n">
         <v>0.7538244430309502</v>
       </c>
+      <c r="BS29" t="n">
+        <v/>
+      </c>
+      <c r="BT29" t="n">
+        <v/>
+      </c>
+      <c r="BU29" t="n">
+        <v/>
+      </c>
       <c r="BV29" t="n">
         <v>-0.8195829029400358</v>
       </c>
@@ -16099,6 +20458,15 @@
       <c r="CE29" t="n">
         <v>0.6720700351151183</v>
       </c>
+      <c r="CF29" t="n">
+        <v/>
+      </c>
+      <c r="CG29" t="n">
+        <v/>
+      </c>
+      <c r="CH29" t="n">
+        <v/>
+      </c>
       <c r="CI29" t="n">
         <v>-0.6080021793231648</v>
       </c>
@@ -16126,6 +20494,15 @@
       <c r="CQ29" t="n">
         <v>0.09734234636130536</v>
       </c>
+      <c r="CR29" t="n">
+        <v/>
+      </c>
+      <c r="CS29" t="n">
+        <v/>
+      </c>
+      <c r="CT29" t="n">
+        <v/>
+      </c>
       <c r="CU29" t="n">
         <v>-0.9091879400759206</v>
       </c>
@@ -16252,24 +20629,102 @@
       <c r="EJ29" t="n">
         <v>-0.08202542776062594</v>
       </c>
+      <c r="EK29" t="n">
+        <v/>
+      </c>
+      <c r="EL29" t="n">
+        <v/>
+      </c>
+      <c r="EM29" t="n">
+        <v/>
+      </c>
+      <c r="EN29" t="n">
+        <v/>
+      </c>
+      <c r="EO29" t="n">
+        <v/>
+      </c>
       <c r="EP29" t="n">
         <v>0.7378375057432205</v>
       </c>
       <c r="EQ29" t="n">
         <v>0.6613158241182694</v>
       </c>
+      <c r="ER29" t="n">
+        <v/>
+      </c>
+      <c r="ES29" t="n">
+        <v/>
+      </c>
+      <c r="ET29" t="n">
+        <v/>
+      </c>
+      <c r="EU29" t="n">
+        <v/>
+      </c>
+      <c r="EV29" t="n">
+        <v/>
+      </c>
       <c r="EW29" t="n">
         <v>-0.5227548036154153</v>
       </c>
+      <c r="EX29" t="n">
+        <v/>
+      </c>
+      <c r="EY29" t="n">
+        <v/>
+      </c>
+      <c r="EZ29" t="n">
+        <v/>
+      </c>
+      <c r="FA29" t="n">
+        <v/>
+      </c>
+      <c r="FB29" t="n">
+        <v/>
+      </c>
+      <c r="FC29" t="n">
+        <v/>
+      </c>
+      <c r="FD29" t="n">
+        <v/>
+      </c>
+      <c r="FE29" t="n">
+        <v/>
+      </c>
+      <c r="FF29" t="n">
+        <v/>
+      </c>
+      <c r="FG29" t="n">
+        <v/>
+      </c>
       <c r="FH29" t="n">
         <v>-0.503371467155537</v>
       </c>
       <c r="FI29" t="n">
         <v>0.229821411048848</v>
       </c>
+      <c r="FJ29" t="n">
+        <v/>
+      </c>
+      <c r="FK29" t="n">
+        <v/>
+      </c>
       <c r="FL29" t="n">
         <v>0.8668445145215511</v>
       </c>
+      <c r="FM29" t="n">
+        <v/>
+      </c>
+      <c r="FN29" t="n">
+        <v/>
+      </c>
+      <c r="FO29" t="n">
+        <v/>
+      </c>
+      <c r="FP29" t="n">
+        <v/>
+      </c>
       <c r="FQ29" t="n">
         <v>-0.5574565303183883</v>
       </c>
@@ -16437,6 +20892,2766 @@
       </c>
       <c r="HT29" t="n">
         <v>-0.9465886123762468</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NON_SEIZURE_AVG</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.00209348282757823</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.3427777802391829</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.2816297539608518</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.1002012205925257</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-0.003491545359436687</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.7261595641175612</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.6504478474710265</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.5819730944613779</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.8008787207051403</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-0.2055268215705598</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-0.2663737226354905</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.07352219156378018</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.07750909683931242</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.6017607776804581</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.5098969704555751</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.6635076174943435</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.2360793624603691</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.1358444920648352</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.410352768312066</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.3610935975462942</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.1267970386145607</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.02754104986605131</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.7428393187226411</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.6709550070695196</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.6178133019404434</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.8304101927936486</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>-0.2117111555195282</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>-0.3068814003059888</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.06159838201114267</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.06832848513696829</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.598547562041549</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.5363735912541905</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.6615495739522871</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.2368174420069546</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0.1573823698180414</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>-0.06834993391500414</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>-0.2637871773379533</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>-0.3431024685215817</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0.5120064628074366</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0.4717170655342938</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0.2035542354117051</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0.5849884649461042</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>-0.4702674288042427</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>-0.4981501051028294</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>-0.238765257780969</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>-0.2510677931682942</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0.3982708920717103</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0.1689197812457608</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0.4360386289630233</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>-0.08277337697477397</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>-0.1469502991952567</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>-0.2974873974764844</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>-0.348925878486914</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0.5924605646120733</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0.4200274177555713</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0.3707393628207229</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0.6588716914962575</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>-0.4347509825708393</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>-0.5174054024595478</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>-0.1629801686644298</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>-0.1889862098286465</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>0.43370554999386</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>0.3459162338846367</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>0.4761674577170708</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>0.01682352897455027</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>-0.03419655773211315</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>-0.03702446044382102</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>0.6771130412060383</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>0.5819640550077423</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>0.4489360530558744</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>0.7766769460679031</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>-0.3184664695760731</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>-0.2989752608161892</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>0.06931483940166801</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>0.06826374674167301</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>0.6483967211379695</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>0.5287977045773762</v>
+      </c>
+      <c r="CB30" t="n">
+        <v>0.6723259795139528</v>
+      </c>
+      <c r="CC30" t="n">
+        <v>0.2635092867496374</v>
+      </c>
+      <c r="CD30" t="n">
+        <v>0.1615984373406898</v>
+      </c>
+      <c r="CE30" t="n">
+        <v>0.7110294589351641</v>
+      </c>
+      <c r="CF30" t="n">
+        <v>0.6750631113997965</v>
+      </c>
+      <c r="CG30" t="n">
+        <v>0.6140470602380463</v>
+      </c>
+      <c r="CH30" t="n">
+        <v>0.8140108223069934</v>
+      </c>
+      <c r="CI30" t="n">
+        <v>-0.2161859611932117</v>
+      </c>
+      <c r="CJ30" t="n">
+        <v>-0.3036879559119792</v>
+      </c>
+      <c r="CK30" t="n">
+        <v>0.09174968178053303</v>
+      </c>
+      <c r="CL30" t="n">
+        <v>0.1417356275573247</v>
+      </c>
+      <c r="CM30" t="n">
+        <v>0.6122953090909787</v>
+      </c>
+      <c r="CN30" t="n">
+        <v>0.6388173015479597</v>
+      </c>
+      <c r="CO30" t="n">
+        <v>0.6789631553651702</v>
+      </c>
+      <c r="CP30" t="n">
+        <v>0.2996180981591408</v>
+      </c>
+      <c r="CQ30" t="n">
+        <v>0.2063827759518475</v>
+      </c>
+      <c r="CR30" t="n">
+        <v>0.132561121219098</v>
+      </c>
+      <c r="CS30" t="n">
+        <v>-0.05653696809023824</v>
+      </c>
+      <c r="CT30" t="n">
+        <v>0.3712317709106367</v>
+      </c>
+      <c r="CU30" t="n">
+        <v>-0.7463395198670015</v>
+      </c>
+      <c r="CV30" t="n">
+        <v>-0.7867024262787687</v>
+      </c>
+      <c r="CW30" t="n">
+        <v>-0.5681514562928169</v>
+      </c>
+      <c r="CX30" t="n">
+        <v>-0.5867822760897157</v>
+      </c>
+      <c r="CY30" t="n">
+        <v>0.1030584515611612</v>
+      </c>
+      <c r="CZ30" t="n">
+        <v>-0.09979248574167536</v>
+      </c>
+      <c r="DA30" t="n">
+        <v>0.2141573830222516</v>
+      </c>
+      <c r="DB30" t="n">
+        <v>-0.4631249617058852</v>
+      </c>
+      <c r="DC30" t="n">
+        <v>-0.4783305762991049</v>
+      </c>
+      <c r="DD30" t="n">
+        <v>-0.1463077763474166</v>
+      </c>
+      <c r="DE30" t="n">
+        <v>0.2329860820037394</v>
+      </c>
+      <c r="DF30" t="n">
+        <v>-0.7442220824598804</v>
+      </c>
+      <c r="DG30" t="n">
+        <v>-0.7180989791543768</v>
+      </c>
+      <c r="DH30" t="n">
+        <v>-0.5204538404531964</v>
+      </c>
+      <c r="DI30" t="n">
+        <v>-0.5013597072858748</v>
+      </c>
+      <c r="DJ30" t="n">
+        <v>0.2385193765249298</v>
+      </c>
+      <c r="DK30" t="n">
+        <v>-0.06408921920572556</v>
+      </c>
+      <c r="DL30" t="n">
+        <v>0.1340259048814492</v>
+      </c>
+      <c r="DM30" t="n">
+        <v>-0.299864666591387</v>
+      </c>
+      <c r="DN30" t="n">
+        <v>-0.3720668831575972</v>
+      </c>
+      <c r="DO30" t="n">
+        <v>0.3552992504917851</v>
+      </c>
+      <c r="DP30" t="n">
+        <v>-0.6164888792757932</v>
+      </c>
+      <c r="DQ30" t="n">
+        <v>-0.7102700831174561</v>
+      </c>
+      <c r="DR30" t="n">
+        <v>-0.3792899109680035</v>
+      </c>
+      <c r="DS30" t="n">
+        <v>-0.4205868911856588</v>
+      </c>
+      <c r="DT30" t="n">
+        <v>0.1908927848475773</v>
+      </c>
+      <c r="DU30" t="n">
+        <v>0.1382206038061238</v>
+      </c>
+      <c r="DV30" t="n">
+        <v>0.3038635272755562</v>
+      </c>
+      <c r="DW30" t="n">
+        <v>-0.1858996596364126</v>
+      </c>
+      <c r="DX30" t="n">
+        <v>-0.2774931560055726</v>
+      </c>
+      <c r="DY30" t="n">
+        <v>-0.8000152407143439</v>
+      </c>
+      <c r="DZ30" t="n">
+        <v>-0.8401466553178392</v>
+      </c>
+      <c r="EA30" t="n">
+        <v>-0.7115539090178562</v>
+      </c>
+      <c r="EB30" t="n">
+        <v>-0.7530303905846437</v>
+      </c>
+      <c r="EC30" t="n">
+        <v>-0.2641357907553572</v>
+      </c>
+      <c r="ED30" t="n">
+        <v>-0.3639111657835321</v>
+      </c>
+      <c r="EE30" t="n">
+        <v>-0.1544410563926164</v>
+      </c>
+      <c r="EF30" t="n">
+        <v>-0.6634167251523848</v>
+      </c>
+      <c r="EG30" t="n">
+        <v>-0.695282216120553</v>
+      </c>
+      <c r="EH30" t="n">
+        <v>-0.07410804830274605</v>
+      </c>
+      <c r="EI30" t="n">
+        <v>0.4252517917971689</v>
+      </c>
+      <c r="EJ30" t="n">
+        <v>0.2900222096284638</v>
+      </c>
+      <c r="EK30" t="n">
+        <v>0.7699805175323033</v>
+      </c>
+      <c r="EL30" t="n">
+        <v>0.6041863155316328</v>
+      </c>
+      <c r="EM30" t="n">
+        <v>0.7372304468074369</v>
+      </c>
+      <c r="EN30" t="n">
+        <v>0.3542690509069745</v>
+      </c>
+      <c r="EO30" t="n">
+        <v>0.3731051494852646</v>
+      </c>
+      <c r="EP30" t="n">
+        <v>0.391905496543916</v>
+      </c>
+      <c r="EQ30" t="n">
+        <v>0.549697587718307</v>
+      </c>
+      <c r="ER30" t="n">
+        <v>0.7496497846660608</v>
+      </c>
+      <c r="ES30" t="n">
+        <v>0.8085093350244478</v>
+      </c>
+      <c r="ET30" t="n">
+        <v>0.8294483509454744</v>
+      </c>
+      <c r="EU30" t="n">
+        <v>0.3966137061206174</v>
+      </c>
+      <c r="EV30" t="n">
+        <v>0.4492390254223707</v>
+      </c>
+      <c r="EW30" t="n">
+        <v>-0.02281686171915556</v>
+      </c>
+      <c r="EX30" t="n">
+        <v>0.6503680458878554</v>
+      </c>
+      <c r="EY30" t="n">
+        <v>0.532703224988041</v>
+      </c>
+      <c r="EZ30" t="n">
+        <v>0.6738424828515572</v>
+      </c>
+      <c r="FA30" t="n">
+        <v>0.24239118210014</v>
+      </c>
+      <c r="FB30" t="n">
+        <v>0.208475198067926</v>
+      </c>
+      <c r="FC30" t="n">
+        <v>0.6557483978812558</v>
+      </c>
+      <c r="FD30" t="n">
+        <v>0.5821906744419993</v>
+      </c>
+      <c r="FE30" t="n">
+        <v>0.7213374068600662</v>
+      </c>
+      <c r="FF30" t="n">
+        <v>0.1831548966057152</v>
+      </c>
+      <c r="FG30" t="n">
+        <v>0.2554136016782271</v>
+      </c>
+      <c r="FH30" t="n">
+        <v>-0.1290390294270314</v>
+      </c>
+      <c r="FI30" t="n">
+        <v>0.1013199357276349</v>
+      </c>
+      <c r="FJ30" t="n">
+        <v>-0.4849161043703454</v>
+      </c>
+      <c r="FK30" t="n">
+        <v>-0.4410800986322529</v>
+      </c>
+      <c r="FL30" t="n">
+        <v>0.2624042553675511</v>
+      </c>
+      <c r="FM30" t="n">
+        <v>-0.3734585192773299</v>
+      </c>
+      <c r="FN30" t="n">
+        <v>-0.3656176477913692</v>
+      </c>
+      <c r="FO30" t="n">
+        <v>-0.6125617706728171</v>
+      </c>
+      <c r="FP30" t="n">
+        <v>-0.5740123862838293</v>
+      </c>
+      <c r="FQ30" t="n">
+        <v>-0.08352395631040707</v>
+      </c>
+      <c r="FR30" t="n">
+        <v>-0.1844378422953169</v>
+      </c>
+      <c r="FS30" t="n">
+        <v>-0.2920899849493035</v>
+      </c>
+      <c r="FT30" t="n">
+        <v>-0.5794023465335888</v>
+      </c>
+      <c r="FU30" t="n">
+        <v>-0.4964804437243424</v>
+      </c>
+      <c r="FV30" t="n">
+        <v>-0.4993927517965346</v>
+      </c>
+      <c r="FW30" t="n">
+        <v>-0.4339167223622259</v>
+      </c>
+      <c r="FX30" t="n">
+        <v>0.1019343358106114</v>
+      </c>
+      <c r="FY30" t="n">
+        <v>-0.07299926874734752</v>
+      </c>
+      <c r="FZ30" t="n">
+        <v>-0.1989531871489592</v>
+      </c>
+      <c r="GA30" t="n">
+        <v>-0.4835068520760945</v>
+      </c>
+      <c r="GB30" t="n">
+        <v>-0.5253409632198897</v>
+      </c>
+      <c r="GC30" t="n">
+        <v>-0.354126424208154</v>
+      </c>
+      <c r="GD30" t="n">
+        <v>-0.3376103268121581</v>
+      </c>
+      <c r="GE30" t="n">
+        <v>0.2677800181387995</v>
+      </c>
+      <c r="GF30" t="n">
+        <v>-0.5690500559834821</v>
+      </c>
+      <c r="GG30" t="n">
+        <v>-0.631182228553867</v>
+      </c>
+      <c r="GH30" t="n">
+        <v>-0.6952156289628876</v>
+      </c>
+      <c r="GI30" t="n">
+        <v>-0.7518670899284662</v>
+      </c>
+      <c r="GJ30" t="n">
+        <v>-0.6906227978655805</v>
+      </c>
+      <c r="GK30" t="n">
+        <v>-0.6932019401412458</v>
+      </c>
+      <c r="GL30" t="n">
+        <v>-0.2141979392023378</v>
+      </c>
+      <c r="GM30" t="n">
+        <v>-0.2710382939340802</v>
+      </c>
+      <c r="GN30" t="n">
+        <v>-0.2948330778282781</v>
+      </c>
+      <c r="GO30" t="n">
+        <v>-0.2418751922217185</v>
+      </c>
+      <c r="GP30" t="n">
+        <v>-0.2616922758050253</v>
+      </c>
+      <c r="GQ30" t="n">
+        <v>0.06272868010525712</v>
+      </c>
+      <c r="GR30" t="n">
+        <v>0.1117990044045927</v>
+      </c>
+      <c r="GS30" t="n">
+        <v>0.09405166105253725</v>
+      </c>
+      <c r="GT30" t="n">
+        <v>0.1591241828271804</v>
+      </c>
+      <c r="GU30" t="n">
+        <v>0.3056652664294683</v>
+      </c>
+      <c r="GV30" t="n">
+        <v>0.1430845181139003</v>
+      </c>
+      <c r="GW30" t="n">
+        <v>0.4965713356105899</v>
+      </c>
+      <c r="GX30" t="n">
+        <v>-0.7383048274893365</v>
+      </c>
+      <c r="GY30" t="n">
+        <v>-0.6900281461832718</v>
+      </c>
+      <c r="GZ30" t="n">
+        <v>-0.4926762323037706</v>
+      </c>
+      <c r="HA30" t="n">
+        <v>-0.4044870846134635</v>
+      </c>
+      <c r="HB30" t="n">
+        <v>0.4559496483687785</v>
+      </c>
+      <c r="HC30" t="n">
+        <v>0.2760646174905568</v>
+      </c>
+      <c r="HD30" t="n">
+        <v>0.545098155500126</v>
+      </c>
+      <c r="HE30" t="n">
+        <v>-0.4267603565705294</v>
+      </c>
+      <c r="HF30" t="n">
+        <v>-0.5120841798110449</v>
+      </c>
+      <c r="HG30" t="n">
+        <v>-0.1183153898846005</v>
+      </c>
+      <c r="HH30" t="n">
+        <v>-0.1772331218883987</v>
+      </c>
+      <c r="HI30" t="n">
+        <v>-0.8255082194714051</v>
+      </c>
+      <c r="HJ30" t="n">
+        <v>-0.7927458956009393</v>
+      </c>
+      <c r="HK30" t="n">
+        <v>-0.6214289870539333</v>
+      </c>
+      <c r="HL30" t="n">
+        <v>-0.6131954569260031</v>
+      </c>
+      <c r="HM30" t="n">
+        <v>-0.7055821547637657</v>
+      </c>
+      <c r="HN30" t="n">
+        <v>-0.811796046398972</v>
+      </c>
+      <c r="HO30" t="n">
+        <v>-0.4342330768070081</v>
+      </c>
+      <c r="HP30" t="n">
+        <v>-0.5246627719113724</v>
+      </c>
+      <c r="HQ30" t="n">
+        <v>-0.8029368042614642</v>
+      </c>
+      <c r="HR30" t="n">
+        <v>-0.8128397459559888</v>
+      </c>
+      <c r="HS30" t="n">
+        <v>-0.6646750584494113</v>
+      </c>
+      <c r="HT30" t="n">
+        <v>-0.6555528283164598</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SEIZURE_AVG</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.1196592710054134</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.3215417076544077</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.4139260879689823</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.04897795335338732</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.06998900803977705</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.6136429715882311</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.4668940439152015</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.4404315527555502</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.5683250441825783</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-0.202463243741212</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-0.2757166736511483</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.1137199425956644</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.03039098221181455</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.3430196371242106</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.365636015968424</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.3399145676241608</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.1866218947083513</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.06611668132691323</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.381721618457625</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.5098736355762501</v>
+      </c>
+      <c r="W31" t="n">
+        <v>-0.01214218713889092</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.07452939096596732</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.6462992012768712</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.5089657232824284</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.6054889130311533</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.6231591129422928</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>-0.1301504027272144</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>-0.1971414369187322</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.2130139302602747</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.1811516147618618</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.4449027141561862</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.5000868849994053</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.4282451533549133</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.3256358729187447</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0.2210570868462627</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0.08124738639719553</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>-0.3629753188218309</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>-0.3528534311443425</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0.3522852917902605</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0.1976277227196367</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.2697534384357701</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0.3265363398920838</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>-0.5031087327361863</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>-0.4860349947851823</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>-0.2341040566106809</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>-0.2316270933225915</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0.1960915445354631</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0.1535100025134676</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0.1080514239316478</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>-0.1267744799308697</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>-0.1993218931873727</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>-0.5237294225154571</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>-0.4833722072016853</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0.2504545682082884</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0.1527978361312109</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0.1529417349294571</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0.213679202895562</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>-0.5190373595102057</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>-0.6386623754783635</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>-0.2896450988378064</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>-0.3584902161023694</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>0.06166220362450296</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>0.04114875932468071</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>0.1179582340506479</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>-0.1525614248539874</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>-0.2254667059133386</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>0.01377192904248931</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>0.6578193103328764</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>0.5775698942898811</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>0.5680612326373147</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>0.6391820982492212</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>-0.1428599775029185</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>-0.2063997560286795</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>0.273935904296769</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>0.1880925705073807</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>0.5301551358664013</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>0.5072688175751564</v>
+      </c>
+      <c r="CB31" t="n">
+        <v>0.4304605284614382</v>
+      </c>
+      <c r="CC31" t="n">
+        <v>0.3510771794534138</v>
+      </c>
+      <c r="CD31" t="n">
+        <v>0.2427016921512447</v>
+      </c>
+      <c r="CE31" t="n">
+        <v>0.6498116693298657</v>
+      </c>
+      <c r="CF31" t="n">
+        <v>0.5565736043087469</v>
+      </c>
+      <c r="CG31" t="n">
+        <v>0.6162412592621456</v>
+      </c>
+      <c r="CH31" t="n">
+        <v>0.6331949098408318</v>
+      </c>
+      <c r="CI31" t="n">
+        <v>-0.1213507097726391</v>
+      </c>
+      <c r="CJ31" t="n">
+        <v>-0.3136299601247737</v>
+      </c>
+      <c r="CK31" t="n">
+        <v>0.2426117665949956</v>
+      </c>
+      <c r="CL31" t="n">
+        <v>0.2284576409679518</v>
+      </c>
+      <c r="CM31" t="n">
+        <v>0.5281950869990292</v>
+      </c>
+      <c r="CN31" t="n">
+        <v>0.5268618012083105</v>
+      </c>
+      <c r="CO31" t="n">
+        <v>0.4309441431949706</v>
+      </c>
+      <c r="CP31" t="n">
+        <v>0.3504407774549256</v>
+      </c>
+      <c r="CQ31" t="n">
+        <v>0.2428740800332216</v>
+      </c>
+      <c r="CR31" t="n">
+        <v>0.02342375383322645</v>
+      </c>
+      <c r="CS31" t="n">
+        <v>-0.01334880594491164</v>
+      </c>
+      <c r="CT31" t="n">
+        <v>0.03783531249999703</v>
+      </c>
+      <c r="CU31" t="n">
+        <v>-0.6733164871639566</v>
+      </c>
+      <c r="CV31" t="n">
+        <v>-0.6892591867414568</v>
+      </c>
+      <c r="CW31" t="n">
+        <v>-0.4822825175037559</v>
+      </c>
+      <c r="CX31" t="n">
+        <v>-0.4707900637857027</v>
+      </c>
+      <c r="CY31" t="n">
+        <v>-0.06122266258723197</v>
+      </c>
+      <c r="CZ31" t="n">
+        <v>-0.04331141287557094</v>
+      </c>
+      <c r="DA31" t="n">
+        <v>-0.02426786348839249</v>
+      </c>
+      <c r="DB31" t="n">
+        <v>-0.3341410738311458</v>
+      </c>
+      <c r="DC31" t="n">
+        <v>-0.4130266463167312</v>
+      </c>
+      <c r="DD31" t="n">
+        <v>0.05904054839416136</v>
+      </c>
+      <c r="DE31" t="n">
+        <v>0.08927774735123979</v>
+      </c>
+      <c r="DF31" t="n">
+        <v>-0.6334333068371915</v>
+      </c>
+      <c r="DG31" t="n">
+        <v>-0.6678990895184221</v>
+      </c>
+      <c r="DH31" t="n">
+        <v>-0.3088291917226419</v>
+      </c>
+      <c r="DI31" t="n">
+        <v>-0.3701695541142122</v>
+      </c>
+      <c r="DJ31" t="n">
+        <v>0.149547839733602</v>
+      </c>
+      <c r="DK31" t="n">
+        <v>0.006913965221202061</v>
+      </c>
+      <c r="DL31" t="n">
+        <v>-0.1783668033029256</v>
+      </c>
+      <c r="DM31" t="n">
+        <v>-0.1668169332383214</v>
+      </c>
+      <c r="DN31" t="n">
+        <v>-0.3586750843344449</v>
+      </c>
+      <c r="DO31" t="n">
+        <v>-0.02738542007928624</v>
+      </c>
+      <c r="DP31" t="n">
+        <v>-0.6295641821127252</v>
+      </c>
+      <c r="DQ31" t="n">
+        <v>-0.7409378164360422</v>
+      </c>
+      <c r="DR31" t="n">
+        <v>-0.4803388911112523</v>
+      </c>
+      <c r="DS31" t="n">
+        <v>-0.5253321540474046</v>
+      </c>
+      <c r="DT31" t="n">
+        <v>-0.1195448044251548</v>
+      </c>
+      <c r="DU31" t="n">
+        <v>-0.04419853675547131</v>
+      </c>
+      <c r="DV31" t="n">
+        <v>-0.2511368731594394</v>
+      </c>
+      <c r="DW31" t="n">
+        <v>-0.3377588885029062</v>
+      </c>
+      <c r="DX31" t="n">
+        <v>-0.4083967208635239</v>
+      </c>
+      <c r="DY31" t="n">
+        <v>-0.6952085176185198</v>
+      </c>
+      <c r="DZ31" t="n">
+        <v>-0.7168336212084057</v>
+      </c>
+      <c r="EA31" t="n">
+        <v>-0.5506396873477046</v>
+      </c>
+      <c r="EB31" t="n">
+        <v>-0.5126391646187012</v>
+      </c>
+      <c r="EC31" t="n">
+        <v>-0.150597385113612</v>
+      </c>
+      <c r="ED31" t="n">
+        <v>-0.1356654075952108</v>
+      </c>
+      <c r="EE31" t="n">
+        <v>-0.2469197581112476</v>
+      </c>
+      <c r="EF31" t="n">
+        <v>-0.4469814182839715</v>
+      </c>
+      <c r="EG31" t="n">
+        <v>-0.4714948595457113</v>
+      </c>
+      <c r="EH31" t="n">
+        <v>-0.1086520205397728</v>
+      </c>
+      <c r="EI31" t="n">
+        <v>0.4252362588703858</v>
+      </c>
+      <c r="EJ31" t="n">
+        <v>0.261765825872857</v>
+      </c>
+      <c r="EK31" t="n">
+        <v>0.6254519017489166</v>
+      </c>
+      <c r="EL31" t="n">
+        <v>0.5803612376698974</v>
+      </c>
+      <c r="EM31" t="n">
+        <v>0.4625214953124422</v>
+      </c>
+      <c r="EN31" t="n">
+        <v>0.4518667681638973</v>
+      </c>
+      <c r="EO31" t="n">
+        <v>0.3077879413818141</v>
+      </c>
+      <c r="EP31" t="n">
+        <v>0.452870968259748</v>
+      </c>
+      <c r="EQ31" t="n">
+        <v>0.5455365469032375</v>
+      </c>
+      <c r="ER31" t="n">
+        <v>0.635704641457676</v>
+      </c>
+      <c r="ES31" t="n">
+        <v>0.720163424110805</v>
+      </c>
+      <c r="ET31" t="n">
+        <v>0.4843146521588977</v>
+      </c>
+      <c r="EU31" t="n">
+        <v>0.523062497521145</v>
+      </c>
+      <c r="EV31" t="n">
+        <v>0.4309251802496921</v>
+      </c>
+      <c r="EW31" t="n">
+        <v>-0.009344706902072362</v>
+      </c>
+      <c r="EX31" t="n">
+        <v>0.3966334671646451</v>
+      </c>
+      <c r="EY31" t="n">
+        <v>0.3976808976715359</v>
+      </c>
+      <c r="EZ31" t="n">
+        <v>0.2511824935989284</v>
+      </c>
+      <c r="FA31" t="n">
+        <v>0.266775942367315</v>
+      </c>
+      <c r="FB31" t="n">
+        <v>0.1142134356055646</v>
+      </c>
+      <c r="FC31" t="n">
+        <v>0.3986257862449804</v>
+      </c>
+      <c r="FD31" t="n">
+        <v>0.4087708661490965</v>
+      </c>
+      <c r="FE31" t="n">
+        <v>0.1891601101095595</v>
+      </c>
+      <c r="FF31" t="n">
+        <v>0.212074274488001</v>
+      </c>
+      <c r="FG31" t="n">
+        <v>0.09625444556039875</v>
+      </c>
+      <c r="FH31" t="n">
+        <v>-0.0398857332254823</v>
+      </c>
+      <c r="FI31" t="n">
+        <v>-0.2309914194436204</v>
+      </c>
+      <c r="FJ31" t="n">
+        <v>-0.2675384498360932</v>
+      </c>
+      <c r="FK31" t="n">
+        <v>-0.3790333448624881</v>
+      </c>
+      <c r="FL31" t="n">
+        <v>-0.2250482282349005</v>
+      </c>
+      <c r="FM31" t="n">
+        <v>-0.1991235301299047</v>
+      </c>
+      <c r="FN31" t="n">
+        <v>-0.2693973194561354</v>
+      </c>
+      <c r="FO31" t="n">
+        <v>-0.02385815652942832</v>
+      </c>
+      <c r="FP31" t="n">
+        <v>-0.1215285754224402</v>
+      </c>
+      <c r="FQ31" t="n">
+        <v>-0.1789324926727854</v>
+      </c>
+      <c r="FR31" t="n">
+        <v/>
+      </c>
+      <c r="FS31" t="n">
+        <v/>
+      </c>
+      <c r="FT31" t="n">
+        <v/>
+      </c>
+      <c r="FU31" t="n">
+        <v/>
+      </c>
+      <c r="FV31" t="n">
+        <v/>
+      </c>
+      <c r="FW31" t="n">
+        <v/>
+      </c>
+      <c r="FX31" t="n">
+        <v/>
+      </c>
+      <c r="FY31" t="n">
+        <v/>
+      </c>
+      <c r="FZ31" t="n">
+        <v/>
+      </c>
+      <c r="GA31" t="n">
+        <v/>
+      </c>
+      <c r="GB31" t="n">
+        <v/>
+      </c>
+      <c r="GC31" t="n">
+        <v/>
+      </c>
+      <c r="GD31" t="n">
+        <v/>
+      </c>
+      <c r="GE31" t="n">
+        <v/>
+      </c>
+      <c r="GF31" t="n">
+        <v/>
+      </c>
+      <c r="GG31" t="n">
+        <v/>
+      </c>
+      <c r="GH31" t="n">
+        <v/>
+      </c>
+      <c r="GI31" t="n">
+        <v/>
+      </c>
+      <c r="GJ31" t="n">
+        <v/>
+      </c>
+      <c r="GK31" t="n">
+        <v/>
+      </c>
+      <c r="GL31" t="n">
+        <v/>
+      </c>
+      <c r="GM31" t="n">
+        <v/>
+      </c>
+      <c r="GN31" t="n">
+        <v/>
+      </c>
+      <c r="GO31" t="n">
+        <v/>
+      </c>
+      <c r="GP31" t="n">
+        <v/>
+      </c>
+      <c r="GQ31" t="n">
+        <v/>
+      </c>
+      <c r="GR31" t="n">
+        <v/>
+      </c>
+      <c r="GS31" t="n">
+        <v/>
+      </c>
+      <c r="GT31" t="n">
+        <v/>
+      </c>
+      <c r="GU31" t="n">
+        <v/>
+      </c>
+      <c r="GV31" t="n">
+        <v/>
+      </c>
+      <c r="GW31" t="n">
+        <v/>
+      </c>
+      <c r="GX31" t="n">
+        <v/>
+      </c>
+      <c r="GY31" t="n">
+        <v/>
+      </c>
+      <c r="GZ31" t="n">
+        <v/>
+      </c>
+      <c r="HA31" t="n">
+        <v/>
+      </c>
+      <c r="HB31" t="n">
+        <v/>
+      </c>
+      <c r="HC31" t="n">
+        <v/>
+      </c>
+      <c r="HD31" t="n">
+        <v/>
+      </c>
+      <c r="HE31" t="n">
+        <v/>
+      </c>
+      <c r="HF31" t="n">
+        <v/>
+      </c>
+      <c r="HG31" t="n">
+        <v/>
+      </c>
+      <c r="HH31" t="n">
+        <v/>
+      </c>
+      <c r="HI31" t="n">
+        <v/>
+      </c>
+      <c r="HJ31" t="n">
+        <v/>
+      </c>
+      <c r="HK31" t="n">
+        <v/>
+      </c>
+      <c r="HL31" t="n">
+        <v/>
+      </c>
+      <c r="HM31" t="n">
+        <v/>
+      </c>
+      <c r="HN31" t="n">
+        <v/>
+      </c>
+      <c r="HO31" t="n">
+        <v/>
+      </c>
+      <c r="HP31" t="n">
+        <v/>
+      </c>
+      <c r="HQ31" t="n">
+        <v/>
+      </c>
+      <c r="HR31" t="n">
+        <v/>
+      </c>
+      <c r="HS31" t="n">
+        <v/>
+      </c>
+      <c r="HT31" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>APRAXIA_AVG</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.02463342057055237</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.366969721638405</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.3452122963795596</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.007171733189815965</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.01873273963470384</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.6548549288831078</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.5876900386920478</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.5293670904765834</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.7584396751605179</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-0.2501584446864109</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-0.3455840101230955</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.1406163225345963</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-0.04010614488992432</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.496860918707863</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.419657060390033</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.5592230070161078</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.2010483844642455</v>
+      </c>
+      <c r="T32" t="n">
+        <v>-0.01167896853460547</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.4029673201128961</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.4036590978871412</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.007542311912708222</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.04668261967542051</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0.6504062653857924</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.5788768442765698</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.6131744502512271</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.7995487561196761</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>-0.2276862507283071</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>-0.3677291985178363</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.120572516771549</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>-0.02675171614981827</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.495468375278568</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.4655609456724172</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.5844203062578356</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.2077020871343444</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.01573901166575273</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0.008853117787438339</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>-0.3150878551588622</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>-0.2962911276005592</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0.4556792622885775</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0.2938891707150157</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0.2351773929786753</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0.5221309741172214</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>-0.4758663033449482</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>-0.5106579991120055</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>-0.1563674753756402</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>-0.3054513271175086</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0.3016122750867898</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0.1603221817096445</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0.3446999781107468</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>-0.08399874370831334</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>-0.2540438482354409</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>-0.3840088144433249</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>-0.3504839632267698</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0.4784386066200082</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0.3270027462497817</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0.3015686136400236</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0.5728064252814294</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>-0.4733573412550688</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>-0.6188632352413777</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>-0.1785207460517469</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>-0.3271894902468467</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>0.3213937218936817</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>0.263215212116622</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>0.4101932922566657</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>-0.05092056986537152</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>-0.1920930379518196</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>0.0702452195331786</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>0.6515566233184003</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>0.5862657497125637</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>0.5943232407559353</v>
+      </c>
+      <c r="BU32" t="n">
+        <v>0.7914756069105375</v>
+      </c>
+      <c r="BV32" t="n">
+        <v>-0.282338959392125</v>
+      </c>
+      <c r="BW32" t="n">
+        <v>-0.2954612317004608</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>0.2193780012089496</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>0.0496156834779015</v>
+      </c>
+      <c r="BZ32" t="n">
+        <v>0.6252899252127176</v>
+      </c>
+      <c r="CA32" t="n">
+        <v>0.5419798207551617</v>
+      </c>
+      <c r="CB32" t="n">
+        <v>0.635076926077434</v>
+      </c>
+      <c r="CC32" t="n">
+        <v>0.2948522579361212</v>
+      </c>
+      <c r="CD32" t="n">
+        <v>0.09612896114559059</v>
+      </c>
+      <c r="CE32" t="n">
+        <v>0.6400184155499734</v>
+      </c>
+      <c r="CF32" t="n">
+        <v>0.6009284638280898</v>
+      </c>
+      <c r="CG32" t="n">
+        <v>0.6509643891505795</v>
+      </c>
+      <c r="CH32" t="n">
+        <v>0.7873076628210991</v>
+      </c>
+      <c r="CI32" t="n">
+        <v>-0.2455082231542048</v>
+      </c>
+      <c r="CJ32" t="n">
+        <v>-0.4505880148043202</v>
+      </c>
+      <c r="CK32" t="n">
+        <v>0.1529584569216559</v>
+      </c>
+      <c r="CL32" t="n">
+        <v>0.0298012938668172</v>
+      </c>
+      <c r="CM32" t="n">
+        <v>0.5283361645032718</v>
+      </c>
+      <c r="CN32" t="n">
+        <v>0.5707355971976427</v>
+      </c>
+      <c r="CO32" t="n">
+        <v>0.6103259106899359</v>
+      </c>
+      <c r="CP32" t="n">
+        <v>0.2871863415768989</v>
+      </c>
+      <c r="CQ32" t="n">
+        <v>0.06389460680527671</v>
+      </c>
+      <c r="CR32" t="n">
+        <v>0.1158633723800983</v>
+      </c>
+      <c r="CS32" t="n">
+        <v>0.02873068670476051</v>
+      </c>
+      <c r="CT32" t="n">
+        <v>0.3153338739925038</v>
+      </c>
+      <c r="CU32" t="n">
+        <v>-0.7176934878146813</v>
+      </c>
+      <c r="CV32" t="n">
+        <v>-0.7567782911128609</v>
+      </c>
+      <c r="CW32" t="n">
+        <v>-0.5086568786420611</v>
+      </c>
+      <c r="CX32" t="n">
+        <v>-0.6024919540492059</v>
+      </c>
+      <c r="CY32" t="n">
+        <v>0.02230239010796383</v>
+      </c>
+      <c r="CZ32" t="n">
+        <v>-0.08481785124192585</v>
+      </c>
+      <c r="DA32" t="n">
+        <v>0.1331881661661285</v>
+      </c>
+      <c r="DB32" t="n">
+        <v>-0.4255939716807817</v>
+      </c>
+      <c r="DC32" t="n">
+        <v>-0.5370636004654873</v>
+      </c>
+      <c r="DD32" t="n">
+        <v>-0.06885116332865283</v>
+      </c>
+      <c r="DE32" t="n">
+        <v>0.246635950397351</v>
+      </c>
+      <c r="DF32" t="n">
+        <v>-0.6900802399581822</v>
+      </c>
+      <c r="DG32" t="n">
+        <v>-0.7135140645970242</v>
+      </c>
+      <c r="DH32" t="n">
+        <v>-0.4105601167167187</v>
+      </c>
+      <c r="DI32" t="n">
+        <v>-0.5260663451492317</v>
+      </c>
+      <c r="DJ32" t="n">
+        <v>0.1992469533942651</v>
+      </c>
+      <c r="DK32" t="n">
+        <v>-0.06575385676001717</v>
+      </c>
+      <c r="DL32" t="n">
+        <v>0.05843565229552496</v>
+      </c>
+      <c r="DM32" t="n">
+        <v>-0.2722552700461321</v>
+      </c>
+      <c r="DN32" t="n">
+        <v>-0.487519828195782</v>
+      </c>
+      <c r="DO32" t="n">
+        <v>0.3203929554530196</v>
+      </c>
+      <c r="DP32" t="n">
+        <v>-0.6536978418466879</v>
+      </c>
+      <c r="DQ32" t="n">
+        <v>-0.7473331740059589</v>
+      </c>
+      <c r="DR32" t="n">
+        <v>-0.3838034796642232</v>
+      </c>
+      <c r="DS32" t="n">
+        <v>-0.5480872889704774</v>
+      </c>
+      <c r="DT32" t="n">
+        <v>0.07723078343988141</v>
+      </c>
+      <c r="DU32" t="n">
+        <v>0.1001491469293349</v>
+      </c>
+      <c r="DV32" t="n">
+        <v>0.1897743289710174</v>
+      </c>
+      <c r="DW32" t="n">
+        <v>-0.234549973897074</v>
+      </c>
+      <c r="DX32" t="n">
+        <v>-0.4262075547120752</v>
+      </c>
+      <c r="DY32" t="n">
+        <v>-0.7901157862789748</v>
+      </c>
+      <c r="DZ32" t="n">
+        <v>-0.8370176844808119</v>
+      </c>
+      <c r="EA32" t="n">
+        <v>-0.6595738588842263</v>
+      </c>
+      <c r="EB32" t="n">
+        <v>-0.768531793170771</v>
+      </c>
+      <c r="EC32" t="n">
+        <v>-0.304681372979951</v>
+      </c>
+      <c r="ED32" t="n">
+        <v>-0.3872951318100799</v>
+      </c>
+      <c r="EE32" t="n">
+        <v>-0.2049557344784945</v>
+      </c>
+      <c r="EF32" t="n">
+        <v>-0.6396847582187695</v>
+      </c>
+      <c r="EG32" t="n">
+        <v>-0.7298596059239586</v>
+      </c>
+      <c r="EH32" t="n">
+        <v>-0.1461160586505863</v>
+      </c>
+      <c r="EI32" t="n">
+        <v>0.4964238758458416</v>
+      </c>
+      <c r="EJ32" t="n">
+        <v>0.2326580997619257</v>
+      </c>
+      <c r="EK32" t="n">
+        <v>0.7057200560209241</v>
+      </c>
+      <c r="EL32" t="n">
+        <v>0.6336559319092162</v>
+      </c>
+      <c r="EM32" t="n">
+        <v>0.6841238924609042</v>
+      </c>
+      <c r="EN32" t="n">
+        <v>0.4566022676132969</v>
+      </c>
+      <c r="EO32" t="n">
+        <v>0.3214326308030492</v>
+      </c>
+      <c r="EP32" t="n">
+        <v>0.5456725298822711</v>
+      </c>
+      <c r="EQ32" t="n">
+        <v>0.5478946473640284</v>
+      </c>
+      <c r="ER32" t="n">
+        <v>0.7407452942275926</v>
+      </c>
+      <c r="ES32" t="n">
+        <v>0.8008036649154842</v>
+      </c>
+      <c r="ET32" t="n">
+        <v>0.7353283950761627</v>
+      </c>
+      <c r="EU32" t="n">
+        <v>0.5469237072310431</v>
+      </c>
+      <c r="EV32" t="n">
+        <v>0.4818724232517662</v>
+      </c>
+      <c r="EW32" t="n">
+        <v>-0.2159107854465533</v>
+      </c>
+      <c r="EX32" t="n">
+        <v>0.4497603552457185</v>
+      </c>
+      <c r="EY32" t="n">
+        <v>0.3467530455787623</v>
+      </c>
+      <c r="EZ32" t="n">
+        <v>0.4264745287908535</v>
+      </c>
+      <c r="FA32" t="n">
+        <v>0.1056310454651543</v>
+      </c>
+      <c r="FB32" t="n">
+        <v>0.001674095061716723</v>
+      </c>
+      <c r="FC32" t="n">
+        <v>0.5902336140578951</v>
+      </c>
+      <c r="FD32" t="n">
+        <v>0.5482667328719877</v>
+      </c>
+      <c r="FE32" t="n">
+        <v>0.5613638168577799</v>
+      </c>
+      <c r="FF32" t="n">
+        <v>0.2446201556557702</v>
+      </c>
+      <c r="FG32" t="n">
+        <v>0.1424396595107921</v>
+      </c>
+      <c r="FH32" t="n">
+        <v>-0.09513825489540517</v>
+      </c>
+      <c r="FI32" t="n">
+        <v>0.0007722617237165712</v>
+      </c>
+      <c r="FJ32" t="n">
+        <v>-0.3926976813487998</v>
+      </c>
+      <c r="FK32" t="n">
+        <v>-0.4907757426897256</v>
+      </c>
+      <c r="FL32" t="n">
+        <v>0.1249741801162091</v>
+      </c>
+      <c r="FM32" t="n">
+        <v>-0.2929880759612105</v>
+      </c>
+      <c r="FN32" t="n">
+        <v>-0.3742855867187758</v>
+      </c>
+      <c r="FO32" t="n">
+        <v>-0.3997755274713845</v>
+      </c>
+      <c r="FP32" t="n">
+        <v>-0.5130854473354737</v>
+      </c>
+      <c r="FQ32" t="n">
+        <v>-0.2435796673156799</v>
+      </c>
+      <c r="FR32" t="n">
+        <v>-0.2207648483611294</v>
+      </c>
+      <c r="FS32" t="n">
+        <v>-0.2568113818729038</v>
+      </c>
+      <c r="FT32" t="n">
+        <v>-0.5169610749055412</v>
+      </c>
+      <c r="FU32" t="n">
+        <v>-0.4195153813790293</v>
+      </c>
+      <c r="FV32" t="n">
+        <v>-0.3926174034450654</v>
+      </c>
+      <c r="FW32" t="n">
+        <v>-0.3436622444748205</v>
+      </c>
+      <c r="FX32" t="n">
+        <v>0.1049116836258465</v>
+      </c>
+      <c r="FY32" t="n">
+        <v>-0.03854172535909457</v>
+      </c>
+      <c r="FZ32" t="n">
+        <v>-0.1657550846969139</v>
+      </c>
+      <c r="GA32" t="n">
+        <v>-0.4037089092790805</v>
+      </c>
+      <c r="GB32" t="n">
+        <v>-0.4449099268674081</v>
+      </c>
+      <c r="GC32" t="n">
+        <v>-0.2138911809619333</v>
+      </c>
+      <c r="GD32" t="n">
+        <v>-0.2124073864707988</v>
+      </c>
+      <c r="GE32" t="n">
+        <v>0.2856057999830195</v>
+      </c>
+      <c r="GF32" t="n">
+        <v>-0.5480437246311971</v>
+      </c>
+      <c r="GG32" t="n">
+        <v>-0.5814090403226583</v>
+      </c>
+      <c r="GH32" t="n">
+        <v>-0.6501041370510413</v>
+      </c>
+      <c r="GI32" t="n">
+        <v>-0.6988423955850197</v>
+      </c>
+      <c r="GJ32" t="n">
+        <v>-0.6182074221518493</v>
+      </c>
+      <c r="GK32" t="n">
+        <v>-0.6288434362195172</v>
+      </c>
+      <c r="GL32" t="n">
+        <v>-0.1888490479991231</v>
+      </c>
+      <c r="GM32" t="n">
+        <v>-0.1260687799345436</v>
+      </c>
+      <c r="GN32" t="n">
+        <v>-0.1825496266233069</v>
+      </c>
+      <c r="GO32" t="n">
+        <v>-0.1140933868178831</v>
+      </c>
+      <c r="GP32" t="n">
+        <v>-0.1755053034627614</v>
+      </c>
+      <c r="GQ32" t="n">
+        <v>0.1415933320872554</v>
+      </c>
+      <c r="GR32" t="n">
+        <v>0.1271244418256176</v>
+      </c>
+      <c r="GS32" t="n">
+        <v>0.1615247596394941</v>
+      </c>
+      <c r="GT32" t="n">
+        <v>0.1652303073018182</v>
+      </c>
+      <c r="GU32" t="n">
+        <v>0.2508881169993524</v>
+      </c>
+      <c r="GV32" t="n">
+        <v>0.1231981656892838</v>
+      </c>
+      <c r="GW32" t="n">
+        <v>0.4661090159164487</v>
+      </c>
+      <c r="GX32" t="n">
+        <v>-0.7163605447371799</v>
+      </c>
+      <c r="GY32" t="n">
+        <v>-0.7213776248518735</v>
+      </c>
+      <c r="GZ32" t="n">
+        <v>-0.4631269682535593</v>
+      </c>
+      <c r="HA32" t="n">
+        <v>-0.5389003379449312</v>
+      </c>
+      <c r="HB32" t="n">
+        <v>0.521630107201568</v>
+      </c>
+      <c r="HC32" t="n">
+        <v>0.3949067787145582</v>
+      </c>
+      <c r="HD32" t="n">
+        <v>0.6235114731533536</v>
+      </c>
+      <c r="HE32" t="n">
+        <v>-0.306901827739663</v>
+      </c>
+      <c r="HF32" t="n">
+        <v>-0.4297407427926355</v>
+      </c>
+      <c r="HG32" t="n">
+        <v>0.01557718043284023</v>
+      </c>
+      <c r="HH32" t="n">
+        <v>-0.1511902777486289</v>
+      </c>
+      <c r="HI32" t="n">
+        <v>-0.7916685504759531</v>
+      </c>
+      <c r="HJ32" t="n">
+        <v>-0.7609192620775914</v>
+      </c>
+      <c r="HK32" t="n">
+        <v>-0.555776228253943</v>
+      </c>
+      <c r="HL32" t="n">
+        <v>-0.6374860829604708</v>
+      </c>
+      <c r="HM32" t="n">
+        <v>-0.6606224747863558</v>
+      </c>
+      <c r="HN32" t="n">
+        <v>-0.8215755291660454</v>
+      </c>
+      <c r="HO32" t="n">
+        <v>-0.399793302062198</v>
+      </c>
+      <c r="HP32" t="n">
+        <v>-0.6280360073878298</v>
+      </c>
+      <c r="HQ32" t="n">
+        <v>-0.7756419114490374</v>
+      </c>
+      <c r="HR32" t="n">
+        <v>-0.8027154714626742</v>
+      </c>
+      <c r="HS32" t="n">
+        <v>-0.6298692424124878</v>
+      </c>
+      <c r="HT32" t="n">
+        <v>-0.7004612754863264</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NON_APRAXIA_AVG</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.0816871998118761</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.2976453531366304</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.3699314331929583</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.0198306679144601</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-0.09664061080253752</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.7121501483420756</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.5050206914606999</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.4736228021712824</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.5832648175204824</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-0.1469290129988438</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-0.1759252350403373</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.02650246629615388</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.181336543925652</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.4957062225529751</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.4904576497576141</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.4972364182111375</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.2345320728495073</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.2563316579710409</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.3855054068514338</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.4864426890724834</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.08129314431743115</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.06200081224752661</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0.7698855277350796</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.5756371414173739</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.608431440660519</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.6302092979637324</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>-0.1169782631156003</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>-0.1302266861028608</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.1266782994556724</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.290599938901604</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.5865554349336929</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0.591626584164521</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.5440987730227587</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.3546285306001916</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0.3928050581176051</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>-0.02772287159020757</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>-0.2905837930887051</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>-0.4105550270770571</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0.4360043900235991</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0.3302638937755213</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.2479125169279034</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0.3572628691326764</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>-0.4933733642326425</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>-0.4714097198001828</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>-0.3374897180481993</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>-0.1652677342065488</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0.3337630947279677</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0.1655411501613042</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0.2495570045829414</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>-0.1215760129342708</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>-0.0610906573877994</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>-0.3967241492203253</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>-0.4702207405506346</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0.4214825153986853</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0.2097970823239854</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0.1934156464029599</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0.2466186936288377</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>-0.4637555464099718</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>-0.5017353367495084</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>-0.2596639662558787</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>-0.1716107817234755</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>0.2330556009471721</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>0.169922326081362</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>0.2302767095150228</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>-0.05376588848504038</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>-0.01215692662360342</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>-0.1245482033859527</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>0.6913726435985209</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>0.5732589529837557</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>0.4491252816654038</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>0.6121138187089821</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>-0.2026532395722832</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>-0.218506917822299</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>0.06930519662974186</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>0.2014169142732861</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>0.5688920962122634</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>0.4925852462697763</v>
+      </c>
+      <c r="CB33" t="n">
+        <v>0.4971772995114629</v>
+      </c>
+      <c r="CC33" t="n">
+        <v>0.3046011410783276</v>
+      </c>
+      <c r="CD33" t="n">
+        <v>0.3177799328275726</v>
+      </c>
+      <c r="CE33" t="n">
+        <v>0.7436769560284625</v>
+      </c>
+      <c r="CF33" t="n">
+        <v>0.6114458364141779</v>
+      </c>
+      <c r="CG33" t="n">
+        <v>0.5832350831432757</v>
+      </c>
+      <c r="CH33" t="n">
+        <v>0.6391461621315205</v>
+      </c>
+      <c r="CI33" t="n">
+        <v>-0.09260081993977876</v>
+      </c>
+      <c r="CJ33" t="n">
+        <v>-0.129176386158281</v>
+      </c>
+      <c r="CK33" t="n">
+        <v>0.1535289572673867</v>
+      </c>
+      <c r="CL33" t="n">
+        <v>0.3611487236302005</v>
+      </c>
+      <c r="CM33" t="n">
+        <v>0.6401523695746584</v>
+      </c>
+      <c r="CN33" t="n">
+        <v>0.6212935566745107</v>
+      </c>
+      <c r="CO33" t="n">
+        <v>0.5374089500531967</v>
+      </c>
+      <c r="CP33" t="n">
+        <v>0.3617452499080794</v>
+      </c>
+      <c r="CQ33" t="n">
+        <v>0.4179433494596539</v>
+      </c>
+      <c r="CR33" t="n">
+        <v>0.02753799104973901</v>
+      </c>
+      <c r="CS33" t="n">
+        <v>-0.08577087904587787</v>
+      </c>
+      <c r="CT33" t="n">
+        <v>0.05480377388525265</v>
+      </c>
+      <c r="CU33" t="n">
+        <v>-0.7152092799546107</v>
+      </c>
+      <c r="CV33" t="n">
+        <v>-0.7347846256602845</v>
+      </c>
+      <c r="CW33" t="n">
+        <v>-0.5638064844662893</v>
+      </c>
+      <c r="CX33" t="n">
+        <v>-0.460818984028341</v>
+      </c>
+      <c r="CY33" t="n">
+        <v>0.05341250707496422</v>
+      </c>
+      <c r="CZ33" t="n">
+        <v>-0.06673646207243315</v>
+      </c>
+      <c r="DA33" t="n">
+        <v>0.09681242812431511</v>
+      </c>
+      <c r="DB33" t="n">
+        <v>-0.3918034686854203</v>
+      </c>
+      <c r="DC33" t="n">
+        <v>-0.3450523602739511</v>
+      </c>
+      <c r="DD33" t="n">
+        <v>-0.05489257827442485</v>
+      </c>
+      <c r="DE33" t="n">
+        <v>0.08419110641360018</v>
+      </c>
+      <c r="DF33" t="n">
+        <v>-0.710343007932872</v>
+      </c>
+      <c r="DG33" t="n">
+        <v>-0.6778135568514422</v>
+      </c>
+      <c r="DH33" t="n">
+        <v>-0.4638317337874519</v>
+      </c>
+      <c r="DI33" t="n">
+        <v>-0.3502187695493211</v>
+      </c>
+      <c r="DJ33" t="n">
+        <v>0.2060526633795435</v>
+      </c>
+      <c r="DK33" t="n">
+        <v>0.003077830128489239</v>
+      </c>
+      <c r="DL33" t="n">
+        <v>-0.05784626188848904</v>
+      </c>
+      <c r="DM33" t="n">
+        <v>-0.2124159900326453</v>
+      </c>
+      <c r="DN33" t="n">
+        <v>-0.2154748862719766</v>
+      </c>
+      <c r="DO33" t="n">
+        <v>0.04813783793342658</v>
+      </c>
+      <c r="DP33" t="n">
+        <v>-0.5819633703293629</v>
+      </c>
+      <c r="DQ33" t="n">
+        <v>-0.6920533083821979</v>
+      </c>
+      <c r="DR33" t="n">
+        <v>-0.4662761818957071</v>
+      </c>
+      <c r="DS33" t="n">
+        <v>-0.3572278849112359</v>
+      </c>
+      <c r="DT33" t="n">
+        <v>0.04840249644052604</v>
+      </c>
+      <c r="DU33" t="n">
+        <v>0.01859237938731436</v>
+      </c>
+      <c r="DV33" t="n">
+        <v>-0.06227534190918302</v>
+      </c>
+      <c r="DW33" t="n">
+        <v>-0.264291059938205</v>
+      </c>
+      <c r="DX33" t="n">
+        <v>-0.2115950920755664</v>
+      </c>
+      <c r="DY33" t="n">
+        <v>-0.7163167292540501</v>
+      </c>
+      <c r="DZ33" t="n">
+        <v>-0.7310209209304761</v>
+      </c>
+      <c r="EA33" t="n">
+        <v>-0.6290242684872545</v>
+      </c>
+      <c r="EB33" t="n">
+        <v>-0.5132950135498706</v>
+      </c>
+      <c r="EC33" t="n">
+        <v>-0.1093769411363484</v>
+      </c>
+      <c r="ED33" t="n">
+        <v>-0.1254559299110529</v>
+      </c>
+      <c r="EE33" t="n">
+        <v>-0.1760698520273475</v>
+      </c>
+      <c r="EF33" t="n">
+        <v>-0.4946826525233582</v>
+      </c>
+      <c r="EG33" t="n">
+        <v>-0.446922068672691</v>
+      </c>
+      <c r="EH33" t="n">
+        <v>-0.01576334325188698</v>
+      </c>
+      <c r="EI33" t="n">
+        <v>0.33627244822011</v>
+      </c>
+      <c r="EJ33" t="n">
+        <v>0.3358256618523302</v>
+      </c>
+      <c r="EK33" t="n">
+        <v>0.6688334555308194</v>
+      </c>
+      <c r="EL33" t="n">
+        <v>0.5514560751438988</v>
+      </c>
+      <c r="EM33" t="n">
+        <v>0.4828464990748221</v>
+      </c>
+      <c r="EN33" t="n">
+        <v>0.3695266448538994</v>
+      </c>
+      <c r="EO33" t="n">
+        <v>0.3477614873854628</v>
+      </c>
+      <c r="EP33" t="n">
+        <v>0.2555817206104848</v>
+      </c>
+      <c r="EQ33" t="n">
+        <v>0.5481369757473419</v>
+      </c>
+      <c r="ER33" t="n">
+        <v>0.6323241685314588</v>
+      </c>
+      <c r="ES33" t="n">
+        <v>0.7182639361175081</v>
+      </c>
+      <c r="ET33" t="n">
+        <v>0.5345092425626208</v>
+      </c>
+      <c r="EU33" t="n">
+        <v>0.4004283756618146</v>
+      </c>
+      <c r="EV33" t="n">
+        <v>0.3997237376859683</v>
+      </c>
+      <c r="EW33" t="n">
+        <v>0.2309000181890845</v>
+      </c>
+      <c r="EX33" t="n">
+        <v>0.5518069308702473</v>
+      </c>
+      <c r="EY33" t="n">
+        <v>0.5515338264082362</v>
+      </c>
+      <c r="EZ33" t="n">
+        <v>0.431547653328299</v>
+      </c>
+      <c r="FA33" t="n">
+        <v>0.3922985413655196</v>
+      </c>
+      <c r="FB33" t="n">
+        <v>0.2909082520649168</v>
+      </c>
+      <c r="FC33" t="n">
+        <v>0.4318768305223774</v>
+      </c>
+      <c r="FD33" t="n">
+        <v>0.4219604327328167</v>
+      </c>
+      <c r="FE33" t="n">
+        <v>0.2799186114365664</v>
+      </c>
+      <c r="FF33" t="n">
+        <v>0.15964747913118</v>
+      </c>
+      <c r="FG33" t="n">
+        <v>0.1820150778993074</v>
+      </c>
+      <c r="FH33" t="n">
+        <v>-0.08969114274014421</v>
+      </c>
+      <c r="FI33" t="n">
+        <v>-0.07761421400778448</v>
+      </c>
+      <c r="FJ33" t="n">
+        <v>-0.3287972651020589</v>
+      </c>
+      <c r="FK33" t="n">
+        <v>-0.3281025898337863</v>
+      </c>
+      <c r="FL33" t="n">
+        <v>-0.01263959387051858</v>
+      </c>
+      <c r="FM33" t="n">
+        <v>-0.2541134301996698</v>
+      </c>
+      <c r="FN33" t="n">
+        <v>-0.2519741415879461</v>
+      </c>
+      <c r="FO33" t="n">
+        <v>-0.1564954139963787</v>
+      </c>
+      <c r="FP33" t="n">
+        <v>-0.1311144393898214</v>
+      </c>
+      <c r="FQ33" t="n">
+        <v>0.0290878574473372</v>
+      </c>
+      <c r="FR33" t="n">
+        <v>-0.05729332106497309</v>
+      </c>
+      <c r="FS33" t="n">
+        <v>-0.4155650957167028</v>
+      </c>
+      <c r="FT33" t="n">
+        <v>-0.7979467972317547</v>
+      </c>
+      <c r="FU33" t="n">
+        <v>-0.7658581619329383</v>
+      </c>
+      <c r="FV33" t="n">
+        <v>-0.8731064710266772</v>
+      </c>
+      <c r="FW33" t="n">
+        <v>-0.7498073949681451</v>
+      </c>
+      <c r="FX33" t="n">
+        <v>0.09151361845728859</v>
+      </c>
+      <c r="FY33" t="n">
+        <v>-0.1936006706062329</v>
+      </c>
+      <c r="FZ33" t="n">
+        <v>-0.3151465457311177</v>
+      </c>
+      <c r="GA33" t="n">
+        <v>-0.7627996518656432</v>
+      </c>
+      <c r="GB33" t="n">
+        <v>-0.8068495904535755</v>
+      </c>
+      <c r="GC33" t="n">
+        <v>-0.8449497755699268</v>
+      </c>
+      <c r="GD33" t="n">
+        <v>-0.7758206180069155</v>
+      </c>
+      <c r="GE33" t="n">
+        <v>0.2053897816840299</v>
+      </c>
+      <c r="GF33" t="n">
+        <v>-0.6425722157164796</v>
+      </c>
+      <c r="GG33" t="n">
+        <v>-0.8053883873630976</v>
+      </c>
+      <c r="GH33" t="n">
+        <v>-0.8531058506543496</v>
+      </c>
+      <c r="GI33" t="n">
+        <v>-0.93745352013053</v>
+      </c>
+      <c r="GJ33" t="n">
+        <v>-0.94407661286364</v>
+      </c>
+      <c r="GK33" t="n">
+        <v>-0.9184567038672959</v>
+      </c>
+      <c r="GL33" t="n">
+        <v>-0.3029190584135891</v>
+      </c>
+      <c r="GM33" t="n">
+        <v>-0.7784315929324586</v>
+      </c>
+      <c r="GN33" t="n">
+        <v>-0.6878251570456773</v>
+      </c>
+      <c r="GO33" t="n">
+        <v>-0.6891115111351425</v>
+      </c>
+      <c r="GP33" t="n">
+        <v>-0.5633466790029493</v>
+      </c>
+      <c r="GQ33" t="n">
+        <v>-0.2132976018317367</v>
+      </c>
+      <c r="GR33" t="n">
+        <v>0.05815997343100562</v>
+      </c>
+      <c r="GS33" t="n">
+        <v>-0.1421041840018115</v>
+      </c>
+      <c r="GT33" t="n">
+        <v>0.137752747165948</v>
+      </c>
+      <c r="GU33" t="n">
+        <v>0.497385289434874</v>
+      </c>
+      <c r="GV33" t="n">
+        <v>0.2126867516000581</v>
+      </c>
+      <c r="GW33" t="n">
+        <v>0.6031894545400841</v>
+      </c>
+      <c r="GX33" t="n">
+        <v>-0.815109817121885</v>
+      </c>
+      <c r="GY33" t="n">
+        <v>-0.580304970843166</v>
+      </c>
+      <c r="GZ33" t="n">
+        <v>-0.5960986564795103</v>
+      </c>
+      <c r="HA33" t="n">
+        <v>0.0659593020466728</v>
+      </c>
+      <c r="HB33" t="n">
+        <v>0.2260680424540154</v>
+      </c>
+      <c r="HC33" t="n">
+        <v>-0.1398829467934481</v>
+      </c>
+      <c r="HD33" t="n">
+        <v>0.2706515437138291</v>
+      </c>
+      <c r="HE33" t="n">
+        <v>-0.8462652074785622</v>
+      </c>
+      <c r="HF33" t="n">
+        <v>-0.8002862093754779</v>
+      </c>
+      <c r="HG33" t="n">
+        <v>-0.5869393859956432</v>
+      </c>
+      <c r="HH33" t="n">
+        <v>-0.2683830763775927</v>
+      </c>
+      <c r="HI33" t="n">
+        <v>-0.9439470609554874</v>
+      </c>
+      <c r="HJ33" t="n">
+        <v>-0.9041391129326575</v>
+      </c>
+      <c r="HK33" t="n">
+        <v>-0.8512136428538997</v>
+      </c>
+      <c r="HL33" t="n">
+        <v>-0.5281782658053659</v>
+      </c>
+      <c r="HM33" t="n">
+        <v>-0.8629410346847012</v>
+      </c>
+      <c r="HN33" t="n">
+        <v>-0.7775678567142145</v>
+      </c>
+      <c r="HO33" t="n">
+        <v>-0.5547722884138432</v>
+      </c>
+      <c r="HP33" t="n">
+        <v>-0.1628564477437715</v>
+      </c>
+      <c r="HQ33" t="n">
+        <v>-0.8984689291049575</v>
+      </c>
+      <c r="HR33" t="n">
+        <v>-0.8482747066825909</v>
+      </c>
+      <c r="HS33" t="n">
+        <v>-0.7864954145786437</v>
+      </c>
+      <c r="HT33" t="n">
+        <v>-0.4983732632219269</v>
       </c>
     </row>
   </sheetData>
